--- a/jogos_2026-07-29.xlsx
+++ b/jogos_2026-07-29.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU18"/>
+  <dimension ref="A1:AU19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -593,22 +593,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G2">
@@ -751,7 +751,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G3">
@@ -902,7 +902,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2026-07-29 13:00:00</t>
+          <t>2026-07-29 12:00:00</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G4">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2026-07-29 14:00:00</t>
+          <t>2026-07-29 13:00:00</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-07-29 14:30:00</t>
+          <t>2026-07-29 14:00:00</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G7">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-07-29 15:00:00</t>
+          <t>2026-07-29 14:30:00</t>
         </is>
       </c>
     </row>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G9">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-07-29 15:15:00</t>
+          <t>2026-07-29 15:00:00</t>
         </is>
       </c>
     </row>
@@ -1892,27 +1892,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G10">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-07-29 19:30:00</t>
+          <t>2026-07-29 15:15:00</t>
         </is>
       </c>
     </row>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G11">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G12">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-07-29 20:00:00</t>
+          <t>2026-07-29 19:30:00</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G13">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-07-29 20:30:00</t>
+          <t>2026-07-29 20:00:00</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G14">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-07-29 21:00:00</t>
+          <t>2026-07-29 20:30:00</t>
         </is>
       </c>
     </row>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G15">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-07-29 21:30:00</t>
+          <t>2026-07-29 21:00:00</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G17">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-07-29 22:00:00</t>
+          <t>2026-07-29 21:30:00</t>
         </is>
       </c>
     </row>
@@ -3196,156 +3196,319 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Utah Royals</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Washington Spirit</t>
+        </is>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>-1</v>
+      </c>
+      <c r="AN18">
+        <v>-1</v>
+      </c>
+      <c r="AO18">
+        <v>-1</v>
+      </c>
+      <c r="AP18">
+        <v>-1</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Bay</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Gotham FC</t>
         </is>
       </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18" t="inlineStr">
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18">
-        <v>0</v>
-      </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18">
-        <v>0</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
-      <c r="U18">
-        <v>0</v>
-      </c>
-      <c r="V18">
-        <v>0</v>
-      </c>
-      <c r="W18">
-        <v>0</v>
-      </c>
-      <c r="X18">
-        <v>0</v>
-      </c>
-      <c r="Y18">
-        <v>0</v>
-      </c>
-      <c r="Z18">
-        <v>0</v>
-      </c>
-      <c r="AA18">
-        <v>0</v>
-      </c>
-      <c r="AB18">
-        <v>0</v>
-      </c>
-      <c r="AC18">
-        <v>0</v>
-      </c>
-      <c r="AD18">
-        <v>0</v>
-      </c>
-      <c r="AE18">
-        <v>0</v>
-      </c>
-      <c r="AF18">
-        <v>0</v>
-      </c>
-      <c r="AG18">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
+      <c r="AI19" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AJ18">
-        <v>0</v>
-      </c>
-      <c r="AK18">
-        <v>0</v>
-      </c>
-      <c r="AL18">
-        <v>0</v>
-      </c>
-      <c r="AM18">
-        <v>-1</v>
-      </c>
-      <c r="AN18">
-        <v>-1</v>
-      </c>
-      <c r="AO18">
-        <v>-1</v>
-      </c>
-      <c r="AP18">
-        <v>-1</v>
-      </c>
-      <c r="AQ18">
-        <v>0</v>
-      </c>
-      <c r="AR18">
-        <v>0</v>
-      </c>
-      <c r="AS18">
-        <v>0</v>
-      </c>
-      <c r="AT18">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>-1</v>
+      </c>
+      <c r="AN19">
+        <v>-1</v>
+      </c>
+      <c r="AO19">
+        <v>-1</v>
+      </c>
+      <c r="AP19">
+        <v>-1</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
         <is>
           <t>2026-07-29 23:00:00</t>
         </is>

--- a/jogos_2026-07-29.xlsx
+++ b/jogos_2026-07-29.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q6">
         <v>0</v>

--- a/jogos_2026-07-29.xlsx
+++ b/jogos_2026-07-29.xlsx
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2141,10 +2141,10 @@
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2304,10 +2304,10 @@
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC12">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -2956,10 +2956,10 @@
         <v>0</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC16">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3119,10 +3119,10 @@
         <v>0</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC17">
         <v>0</v>

--- a/jogos_2026-07-29.xlsx
+++ b/jogos_2026-07-29.xlsx
@@ -807,55 +807,55 @@
         <v>2.94</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1000,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC4">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1489,10 +1489,10 @@
         <v>0</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC7">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>11.9</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1821,10 +1821,10 @@
         <v>0</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -1978,10 +1978,10 @@
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC10">
         <v>0</v>

--- a/jogos_2026-07-29.xlsx
+++ b/jogos_2026-07-29.xlsx
@@ -970,34 +970,34 @@
         <v>4.79</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA4">
         <v>1.98</v>
@@ -1006,19 +1006,19 @@
         <v>1.75</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1133,55 +1133,55 @@
         <v>3.7</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
+        <v>1.67</v>
+      </c>
+      <c r="O6">
+        <v>3.81</v>
+      </c>
+      <c r="P6">
+        <v>4.93</v>
+      </c>
+      <c r="Q6">
+        <v>2.05</v>
+      </c>
+      <c r="R6">
         <v>2.25</v>
       </c>
-      <c r="O6">
-        <v>3.39</v>
-      </c>
-      <c r="P6">
-        <v>3.09</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,80 +1450,80 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="O7">
-        <v>3.81</v>
+        <v>3.39</v>
       </c>
       <c r="P7">
-        <v>4.93</v>
+        <v>3.09</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="AA7">
+        <v>2.05</v>
+      </c>
+      <c r="AB7">
+        <v>1.75</v>
+      </c>
+      <c r="AC7">
+        <v>3.6</v>
+      </c>
+      <c r="AD7">
+        <v>1.25</v>
+      </c>
+      <c r="AE7">
+        <v>1.04</v>
+      </c>
+      <c r="AF7">
+        <v>1.83</v>
+      </c>
+      <c r="AG7">
+        <v>1.87</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
+        <v>1.29</v>
+      </c>
+      <c r="AK7">
         <v>1.8</v>
-      </c>
-      <c r="AB7">
-        <v>1.91</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0</v>
-      </c>
-      <c r="AG7">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>0</v>
-      </c>
-      <c r="AK7">
-        <v>0</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1622,55 +1622,55 @@
         <v>1.76</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1785,40 +1785,40 @@
         <v>18</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC9">
         <v>1.77</v>
@@ -1827,13 +1827,13 @@
         <v>1.95</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1948,34 +1948,34 @@
         <v>8.449999999999999</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA10">
         <v>1.57</v>
@@ -1984,19 +1984,19 @@
         <v>2.25</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2111,34 +2111,34 @@
         <v>4.89</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA11">
         <v>2.05</v>
@@ -2147,19 +2147,19 @@
         <v>1.66</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2274,34 +2274,34 @@
         <v>2.11</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA12">
         <v>1.88</v>
@@ -2310,19 +2310,19 @@
         <v>1.8</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2926,34 +2926,34 @@
         <v>4.46</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA16">
         <v>1.87</v>
@@ -2962,19 +2962,19 @@
         <v>1.8</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3089,34 +3089,34 @@
         <v>1.91</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA17">
         <v>2</v>
@@ -3125,19 +3125,19 @@
         <v>1.68</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL17">
         <v>0</v>

--- a/jogos_2026-07-29.xlsx
+++ b/jogos_2026-07-29.xlsx
@@ -798,31 +798,31 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.43</v>
+        <v>2.21</v>
       </c>
       <c r="O3">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="P3">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="Q3">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="R3">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S3">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="T3">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="U3">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="V3">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W3">
         <v>1.02</v>
@@ -831,7 +831,7 @@
         <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="Z3">
         <v>3</v>
@@ -840,7 +840,7 @@
         <v>2.15</v>
       </c>
       <c r="AB3">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC3">
         <v>3.9</v>
@@ -849,7 +849,7 @@
         <v>1.18</v>
       </c>
       <c r="AE3">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF3">
         <v>1.86</v>
@@ -871,7 +871,7 @@
         <v>1.3</v>
       </c>
       <c r="AK3">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,80 +1287,80 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="O6">
-        <v>3.81</v>
+        <v>3.39</v>
       </c>
       <c r="P6">
-        <v>4.93</v>
+        <v>3.09</v>
       </c>
       <c r="Q6">
+        <v>2.49</v>
+      </c>
+      <c r="R6">
+        <v>2.2</v>
+      </c>
+      <c r="S6">
+        <v>1.39</v>
+      </c>
+      <c r="T6">
+        <v>2.59</v>
+      </c>
+      <c r="U6">
+        <v>2.75</v>
+      </c>
+      <c r="V6">
+        <v>1.4</v>
+      </c>
+      <c r="W6">
+        <v>1.06</v>
+      </c>
+      <c r="X6">
+        <v>1.06</v>
+      </c>
+      <c r="Y6">
+        <v>1.28</v>
+      </c>
+      <c r="Z6">
+        <v>3.23</v>
+      </c>
+      <c r="AA6">
         <v>2.05</v>
       </c>
-      <c r="R6">
-        <v>2.25</v>
-      </c>
-      <c r="S6">
-        <v>1.3</v>
-      </c>
-      <c r="T6">
-        <v>3.3</v>
-      </c>
-      <c r="U6">
-        <v>2.36</v>
-      </c>
-      <c r="V6">
-        <v>1.5</v>
-      </c>
-      <c r="W6">
-        <v>1.08</v>
-      </c>
-      <c r="X6">
-        <v>1.05</v>
-      </c>
-      <c r="Y6">
-        <v>1.19</v>
-      </c>
-      <c r="Z6">
-        <v>3.78</v>
-      </c>
-      <c r="AA6">
+      <c r="AB6">
+        <v>1.75</v>
+      </c>
+      <c r="AC6">
+        <v>3.6</v>
+      </c>
+      <c r="AD6">
+        <v>1.25</v>
+      </c>
+      <c r="AE6">
+        <v>1.04</v>
+      </c>
+      <c r="AF6">
+        <v>1.83</v>
+      </c>
+      <c r="AG6">
+        <v>1.87</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
+        <v>1.29</v>
+      </c>
+      <c r="AK6">
         <v>1.8</v>
-      </c>
-      <c r="AB6">
-        <v>1.91</v>
-      </c>
-      <c r="AC6">
-        <v>3</v>
-      </c>
-      <c r="AD6">
-        <v>1.38</v>
-      </c>
-      <c r="AE6">
-        <v>1.12</v>
-      </c>
-      <c r="AF6">
-        <v>1.72</v>
-      </c>
-      <c r="AG6">
-        <v>2.05</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.14</v>
-      </c>
-      <c r="AK6">
-        <v>2.19</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,65 +1450,65 @@
         </is>
       </c>
       <c r="N7">
+        <v>1.67</v>
+      </c>
+      <c r="O7">
+        <v>3.81</v>
+      </c>
+      <c r="P7">
+        <v>4.93</v>
+      </c>
+      <c r="Q7">
+        <v>2.05</v>
+      </c>
+      <c r="R7">
         <v>2.25</v>
       </c>
-      <c r="O7">
-        <v>3.39</v>
-      </c>
-      <c r="P7">
-        <v>3.09</v>
-      </c>
-      <c r="Q7">
-        <v>2.49</v>
-      </c>
-      <c r="R7">
-        <v>2.2</v>
-      </c>
       <c r="S7">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="T7">
-        <v>2.59</v>
+        <v>3.3</v>
       </c>
       <c r="U7">
-        <v>2.75</v>
+        <v>2.36</v>
       </c>
       <c r="V7">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y7">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="Z7">
-        <v>3.23</v>
+        <v>3.78</v>
       </c>
       <c r="AA7">
+        <v>1.8</v>
+      </c>
+      <c r="AB7">
+        <v>1.91</v>
+      </c>
+      <c r="AC7">
+        <v>3</v>
+      </c>
+      <c r="AD7">
+        <v>1.38</v>
+      </c>
+      <c r="AE7">
+        <v>1.12</v>
+      </c>
+      <c r="AF7">
+        <v>1.72</v>
+      </c>
+      <c r="AG7">
         <v>2.05</v>
       </c>
-      <c r="AB7">
-        <v>1.75</v>
-      </c>
-      <c r="AC7">
-        <v>3.6</v>
-      </c>
-      <c r="AD7">
-        <v>1.25</v>
-      </c>
-      <c r="AE7">
-        <v>1.04</v>
-      </c>
-      <c r="AF7">
-        <v>1.83</v>
-      </c>
-      <c r="AG7">
-        <v>1.87</v>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AK7">
-        <v>1.8</v>
+        <v>2.19</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -3415,55 +3415,55 @@
         <v>0</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL19">
         <v>0</v>

--- a/jogos_2026-07-29.xlsx
+++ b/jogos_2026-07-29.xlsx
@@ -2132,34 +2132,34 @@
         <v>1.03</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z11">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA11">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB11">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AC11">
-        <v>3.62</v>
+        <v>3.8</v>
       </c>
       <c r="AD11">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE11">
         <v>1.04</v>
       </c>
       <c r="AF11">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AG11">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK11">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2280,10 +2280,10 @@
         <v>2.06</v>
       </c>
       <c r="S12">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T12">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="U12">
         <v>2.7</v>
@@ -2292,10 +2292,10 @@
         <v>1.4</v>
       </c>
       <c r="W12">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X12">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y12">
         <v>1.25</v>
@@ -2304,10 +2304,10 @@
         <v>3.3</v>
       </c>
       <c r="AA12">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AB12">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC12">
         <v>3.18</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="O16">
-        <v>3.81</v>
+        <v>3.4</v>
       </c>
       <c r="P16">
-        <v>4.46</v>
+        <v>1.91</v>
       </c>
       <c r="Q16">
-        <v>2.32</v>
+        <v>4.33</v>
       </c>
       <c r="R16">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="S16">
+        <v>1.42</v>
+      </c>
+      <c r="T16">
+        <v>2.65</v>
+      </c>
+      <c r="U16">
+        <v>2.94</v>
+      </c>
+      <c r="V16">
         <v>1.33</v>
       </c>
-      <c r="T16">
-        <v>3</v>
-      </c>
-      <c r="U16">
-        <v>2.6</v>
-      </c>
-      <c r="V16">
-        <v>1.4</v>
-      </c>
       <c r="W16">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="Z16">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="AA16">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AB16">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AC16">
-        <v>3.12</v>
+        <v>3.75</v>
       </c>
       <c r="AD16">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE16">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF16">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AG16">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK16">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,80 +3080,80 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="O17">
-        <v>3.4</v>
+        <v>3.81</v>
       </c>
       <c r="P17">
-        <v>1.91</v>
+        <v>4.46</v>
       </c>
       <c r="Q17">
-        <v>4.33</v>
+        <v>2.32</v>
       </c>
       <c r="R17">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="S17">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="T17">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="U17">
-        <v>2.94</v>
+        <v>2.6</v>
       </c>
       <c r="V17">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W17">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="Z17">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="AA17">
+        <v>1.87</v>
+      </c>
+      <c r="AB17">
+        <v>1.8</v>
+      </c>
+      <c r="AC17">
+        <v>3.12</v>
+      </c>
+      <c r="AD17">
+        <v>1.28</v>
+      </c>
+      <c r="AE17">
+        <v>1.06</v>
+      </c>
+      <c r="AF17">
+        <v>1.78</v>
+      </c>
+      <c r="AG17">
+        <v>1.95</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
+        <v>1.2</v>
+      </c>
+      <c r="AK17">
         <v>2</v>
-      </c>
-      <c r="AB17">
-        <v>1.68</v>
-      </c>
-      <c r="AC17">
-        <v>3.75</v>
-      </c>
-      <c r="AD17">
-        <v>1.25</v>
-      </c>
-      <c r="AE17">
-        <v>1.07</v>
-      </c>
-      <c r="AF17">
-        <v>1.83</v>
-      </c>
-      <c r="AG17">
-        <v>1.85</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.3</v>
-      </c>
-      <c r="AK17">
-        <v>1.25</v>
       </c>
       <c r="AL17">
         <v>0</v>

--- a/jogos_2026-07-29.xlsx
+++ b/jogos_2026-07-29.xlsx
@@ -798,31 +798,31 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="O3">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="P3">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q3">
         <v>2.83</v>
       </c>
       <c r="R3">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S3">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T3">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="U3">
         <v>3</v>
       </c>
       <c r="V3">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W3">
         <v>1.02</v>
@@ -831,25 +831,25 @@
         <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="Z3">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AA3">
         <v>2.15</v>
       </c>
       <c r="AB3">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC3">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AD3">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE3">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF3">
         <v>1.86</v>
@@ -871,7 +871,7 @@
         <v>1.3</v>
       </c>
       <c r="AK3">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="O4">
-        <v>3.57</v>
+        <v>3.6</v>
       </c>
       <c r="P4">
-        <v>4.79</v>
+        <v>4.6</v>
       </c>
       <c r="Q4">
         <v>2.3</v>
@@ -976,34 +976,34 @@
         <v>2.15</v>
       </c>
       <c r="S4">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T4">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="U4">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="V4">
         <v>1.37</v>
       </c>
       <c r="W4">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y4">
         <v>1.26</v>
       </c>
       <c r="Z4">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="AA4">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AB4">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC4">
         <v>3.3</v>
@@ -1012,13 +1012,13 @@
         <v>1.25</v>
       </c>
       <c r="AE4">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF4">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG4">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AK4">
         <v>2</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="O5">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="P5">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="Q5">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="R5">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="S5">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T5">
-        <v>2.88</v>
+        <v>3.18</v>
       </c>
       <c r="U5">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V5">
         <v>1.46</v>
       </c>
       <c r="W5">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
         <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z5">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="AA5">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB5">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AC5">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="AD5">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE5">
         <v>1.11</v>
       </c>
       <c r="AF5">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AG5">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1287,49 +1287,49 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="O6">
-        <v>3.39</v>
+        <v>3.35</v>
       </c>
       <c r="P6">
-        <v>3.09</v>
+        <v>4.1</v>
       </c>
       <c r="Q6">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
       <c r="R6">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="S6">
         <v>1.39</v>
       </c>
       <c r="T6">
-        <v>2.59</v>
+        <v>2.9</v>
       </c>
       <c r="U6">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="V6">
         <v>1.4</v>
       </c>
       <c r="W6">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X6">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z6">
         <v>3.23</v>
       </c>
       <c r="AA6">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AB6">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC6">
         <v>3.6</v>
@@ -1338,7 +1338,7 @@
         <v>1.25</v>
       </c>
       <c r="AE6">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF6">
         <v>1.83</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,19 +1450,19 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="O7">
-        <v>3.81</v>
+        <v>4</v>
       </c>
       <c r="P7">
-        <v>4.93</v>
+        <v>4.4</v>
       </c>
       <c r="Q7">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="R7">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S7">
         <v>1.3</v>
@@ -1471,43 +1471,43 @@
         <v>3.3</v>
       </c>
       <c r="U7">
-        <v>2.36</v>
+        <v>2.63</v>
       </c>
       <c r="V7">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W7">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X7">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
         <v>1.19</v>
       </c>
       <c r="Z7">
-        <v>3.78</v>
+        <v>3.84</v>
       </c>
       <c r="AA7">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AB7">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AC7">
-        <v>3</v>
+        <v>2.59</v>
       </c>
       <c r="AD7">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AE7">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF7">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG7">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK7">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,25 +1613,25 @@
         </is>
       </c>
       <c r="N8">
-        <v>4.26</v>
+        <v>5.75</v>
       </c>
       <c r="O8">
-        <v>3.86</v>
+        <v>4.4</v>
       </c>
       <c r="P8">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="Q8">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="R8">
         <v>2.35</v>
       </c>
       <c r="S8">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T8">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="U8">
         <v>2.45</v>
@@ -1640,37 +1640,37 @@
         <v>1.48</v>
       </c>
       <c r="W8">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z8">
-        <v>3.62</v>
+        <v>3.76</v>
       </c>
       <c r="AA8">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AB8">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AC8">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="AD8">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE8">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF8">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG8">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>2.3</v>
+        <v>1.17</v>
       </c>
       <c r="AK8">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1779,16 +1779,16 @@
         <v>1.08</v>
       </c>
       <c r="O9">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="P9">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="Q9">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="R9">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="S9">
         <v>1.15</v>
@@ -1797,44 +1797,44 @@
         <v>5</v>
       </c>
       <c r="U9">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="V9">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="W9">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="X9">
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z9">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="AA9">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AB9">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AC9">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="AD9">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AE9">
+        <v>1.41</v>
+      </c>
+      <c r="AF9">
+        <v>2.45</v>
+      </c>
+      <c r="AG9">
         <v>1.44</v>
       </c>
-      <c r="AF9">
-        <v>2.38</v>
-      </c>
-      <c r="AG9">
-        <v>1.5</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AK9">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1948,10 +1948,10 @@
         <v>8.449999999999999</v>
       </c>
       <c r="Q10">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R10">
-        <v>2.48</v>
+        <v>2.39</v>
       </c>
       <c r="S10">
         <v>1.28</v>
@@ -1960,31 +1960,31 @@
         <v>3.34</v>
       </c>
       <c r="U10">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="V10">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W10">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X10">
         <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z10">
         <v>4.4</v>
       </c>
       <c r="AA10">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB10">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AC10">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AD10">
         <v>1.49</v>
@@ -1993,10 +1993,10 @@
         <v>1.17</v>
       </c>
       <c r="AF10">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AG10">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AK10">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2111,31 +2111,31 @@
         <v>4.89</v>
       </c>
       <c r="Q11">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R11">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S11">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T11">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="U11">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="V11">
         <v>1.34</v>
       </c>
       <c r="W11">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z11">
         <v>3.2</v>
@@ -2144,19 +2144,19 @@
         <v>2.1</v>
       </c>
       <c r="AB11">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AC11">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD11">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE11">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF11">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AG11">
         <v>1.73</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK11">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2280,10 +2280,10 @@
         <v>2.06</v>
       </c>
       <c r="S12">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T12">
-        <v>2.69</v>
+        <v>2.81</v>
       </c>
       <c r="U12">
         <v>2.7</v>
@@ -2338,7 +2338,7 @@
         <v>1.67</v>
       </c>
       <c r="AK12">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2920,22 +2920,22 @@
         <v>3.8</v>
       </c>
       <c r="O16">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P16">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="Q16">
         <v>4.33</v>
       </c>
       <c r="R16">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S16">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T16">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="U16">
         <v>2.94</v>
@@ -2944,34 +2944,34 @@
         <v>1.33</v>
       </c>
       <c r="W16">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z16">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="AA16">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AB16">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AC16">
         <v>3.75</v>
       </c>
       <c r="AD16">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE16">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF16">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG16">
         <v>1.85</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK16">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3083,10 +3083,10 @@
         <v>1.8</v>
       </c>
       <c r="O17">
-        <v>3.81</v>
+        <v>3.6</v>
       </c>
       <c r="P17">
-        <v>4.46</v>
+        <v>4.42</v>
       </c>
       <c r="Q17">
         <v>2.32</v>
@@ -3104,25 +3104,25 @@
         <v>2.6</v>
       </c>
       <c r="V17">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W17">
         <v>1.06</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y17">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z17">
         <v>3.38</v>
       </c>
       <c r="AA17">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AB17">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AC17">
         <v>3.12</v>
@@ -3134,7 +3134,7 @@
         <v>1.06</v>
       </c>
       <c r="AF17">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG17">
         <v>1.95</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AK17">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3406,28 +3406,28 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q19">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="R19">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="S19">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T19">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="U19">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="V19">
         <v>1.36</v>
@@ -3445,16 +3445,16 @@
         <v>3.04</v>
       </c>
       <c r="AA19">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="AB19">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AC19">
         <v>3.34</v>
       </c>
       <c r="AD19">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AE19">
         <v>1.04</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.21</v>
+        <v>2.1</v>
       </c>
       <c r="AK19">
         <v>1.12</v>

--- a/jogos_2026-07-29.xlsx
+++ b/jogos_2026-07-29.xlsx
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="O13">
         <v>3.2</v>
       </c>
       <c r="P13">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="Q13">
-        <v>2.57</v>
+        <v>2.48</v>
       </c>
       <c r="R13">
-        <v>1.94</v>
+        <v>2.16</v>
       </c>
       <c r="S13">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="T13">
-        <v>2.47</v>
+        <v>2.65</v>
       </c>
       <c r="U13">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="V13">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W13">
         <v>1.01</v>
       </c>
       <c r="X13">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z13">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AA13">
-        <v>2.23</v>
+        <v>1.94</v>
       </c>
       <c r="AB13">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="AC13">
-        <v>3.98</v>
+        <v>4.01</v>
       </c>
       <c r="AD13">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF13">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AG13">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>1.26</v>
       </c>
       <c r="AK13">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2603,7 +2603,7 @@
         <v>1.79</v>
       </c>
       <c r="R14">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="S14">
         <v>1.22</v>
@@ -2612,13 +2612,13 @@
         <v>3.75</v>
       </c>
       <c r="U14">
-        <v>2.22</v>
+        <v>1.92</v>
       </c>
       <c r="V14">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="W14">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X14">
         <v>1.02</v>
@@ -2630,19 +2630,19 @@
         <v>5.27</v>
       </c>
       <c r="AA14">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AB14">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AC14">
         <v>2.28</v>
       </c>
       <c r="AD14">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AE14">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AF14">
         <v>1.65</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AK14">
         <v>2.8</v>

--- a/jogos_2026-07-29.xlsx
+++ b/jogos_2026-07-29.xlsx
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="O13">
         <v>3.2</v>
       </c>
       <c r="P13">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="Q13">
         <v>2.48</v>
@@ -2461,10 +2461,10 @@
         <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z13">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AA13">
         <v>1.94</v>
@@ -2482,7 +2482,7 @@
         <v>1.02</v>
       </c>
       <c r="AF13">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AG13">
         <v>1.87</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK13">
         <v>1.62</v>
@@ -2594,22 +2594,22 @@
         <v>1.33</v>
       </c>
       <c r="O14">
-        <v>5.1</v>
+        <v>5.15</v>
       </c>
       <c r="P14">
-        <v>6.5</v>
+        <v>6.55</v>
       </c>
       <c r="Q14">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R14">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="S14">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="T14">
-        <v>3.75</v>
+        <v>3.92</v>
       </c>
       <c r="U14">
         <v>1.92</v>
@@ -2627,28 +2627,28 @@
         <v>1.09</v>
       </c>
       <c r="Z14">
-        <v>5.27</v>
+        <v>5.44</v>
       </c>
       <c r="AA14">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AB14">
-        <v>2.46</v>
+        <v>2.67</v>
       </c>
       <c r="AC14">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="AD14">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AE14">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF14">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG14">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AK14">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AL14">
         <v>0</v>

--- a/jogos_2026-07-29.xlsx
+++ b/jogos_2026-07-29.xlsx
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="O3">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P3">
         <v>3.1</v>
@@ -810,7 +810,7 @@
         <v>2.83</v>
       </c>
       <c r="R3">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S3">
         <v>1.41</v>
@@ -834,13 +834,13 @@
         <v>1.37</v>
       </c>
       <c r="Z3">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="AA3">
         <v>2.15</v>
       </c>
       <c r="AB3">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC3">
         <v>3.7</v>
@@ -849,7 +849,7 @@
         <v>1.22</v>
       </c>
       <c r="AE3">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF3">
         <v>1.86</v>
@@ -871,7 +871,7 @@
         <v>1.3</v>
       </c>
       <c r="AK3">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="O4">
         <v>3.6</v>
@@ -976,7 +976,7 @@
         <v>2.15</v>
       </c>
       <c r="S4">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T4">
         <v>2.77</v>
@@ -1018,7 +1018,7 @@
         <v>1.86</v>
       </c>
       <c r="AG4">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="O5">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P5">
         <v>3.75</v>
       </c>
       <c r="Q5">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="R5">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S5">
         <v>1.33</v>
@@ -1145,7 +1145,7 @@
         <v>3.18</v>
       </c>
       <c r="U5">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="V5">
         <v>1.46</v>
@@ -1157,10 +1157,10 @@
         <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z5">
-        <v>3.82</v>
+        <v>3.88</v>
       </c>
       <c r="AA5">
         <v>1.8</v>
@@ -1169,19 +1169,19 @@
         <v>2</v>
       </c>
       <c r="AC5">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="AD5">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE5">
         <v>1.11</v>
       </c>
       <c r="AF5">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG5">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="O6">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P6">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Q6">
         <v>2.44</v>
@@ -1302,19 +1302,19 @@
         <v>2.08</v>
       </c>
       <c r="S6">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T6">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U6">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="V6">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W6">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
         <v>1</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK6">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1456,7 +1456,7 @@
         <v>4</v>
       </c>
       <c r="P7">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q7">
         <v>2.07</v>
@@ -1492,7 +1492,7 @@
         <v>1.71</v>
       </c>
       <c r="AB7">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AC7">
         <v>2.59</v>
@@ -1504,7 +1504,7 @@
         <v>1.13</v>
       </c>
       <c r="AF7">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG7">
         <v>2</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="O8">
         <v>4.4</v>
       </c>
       <c r="P8">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="Q8">
         <v>6.5</v>
@@ -1652,19 +1652,19 @@
         <v>3.76</v>
       </c>
       <c r="AA8">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AB8">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AC8">
-        <v>2.72</v>
+        <v>2.85</v>
       </c>
       <c r="AD8">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE8">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF8">
         <v>1.83</v>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="O9">
-        <v>12</v>
+        <v>13.3</v>
       </c>
       <c r="P9">
         <v>26</v>
@@ -1815,16 +1815,16 @@
         <v>7.3</v>
       </c>
       <c r="AA9">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AB9">
         <v>3.5</v>
       </c>
       <c r="AC9">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AD9">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AE9">
         <v>1.41</v>
@@ -1849,7 +1849,7 @@
         <v>1.04</v>
       </c>
       <c r="AK9">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1960,10 +1960,10 @@
         <v>3.34</v>
       </c>
       <c r="U10">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V10">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W10">
         <v>1.09</v>
@@ -1975,7 +1975,7 @@
         <v>1.17</v>
       </c>
       <c r="Z10">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AA10">
         <v>1.6</v>
@@ -1987,10 +1987,10 @@
         <v>2.4</v>
       </c>
       <c r="AD10">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AE10">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF10">
         <v>1.85</v>
@@ -2111,28 +2111,28 @@
         <v>4.89</v>
       </c>
       <c r="Q11">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R11">
         <v>2.1</v>
       </c>
       <c r="S11">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T11">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="U11">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V11">
         <v>1.34</v>
       </c>
       <c r="W11">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
         <v>1.33</v>
@@ -2159,7 +2159,7 @@
         <v>1.97</v>
       </c>
       <c r="AG11">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>1.17</v>
       </c>
       <c r="AK11">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2286,16 +2286,16 @@
         <v>2.81</v>
       </c>
       <c r="U12">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="V12">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W12">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y12">
         <v>1.25</v>
@@ -2338,7 +2338,7 @@
         <v>1.67</v>
       </c>
       <c r="AK12">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2446,7 +2446,7 @@
         <v>1.36</v>
       </c>
       <c r="T13">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="U13">
         <v>3.08</v>
@@ -2600,10 +2600,10 @@
         <v>6.55</v>
       </c>
       <c r="Q14">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="R14">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="S14">
         <v>1.18</v>
@@ -2612,13 +2612,13 @@
         <v>3.92</v>
       </c>
       <c r="U14">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="V14">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W14">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X14">
         <v>1.02</v>
@@ -2642,13 +2642,13 @@
         <v>1.61</v>
       </c>
       <c r="AE14">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AF14">
         <v>1.64</v>
       </c>
       <c r="AG14">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AK14">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O16">
         <v>3.3</v>
@@ -2926,10 +2926,10 @@
         <v>2.05</v>
       </c>
       <c r="Q16">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="R16">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S16">
         <v>1.36</v>
@@ -2941,13 +2941,13 @@
         <v>2.94</v>
       </c>
       <c r="V16">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W16">
         <v>1.05</v>
       </c>
       <c r="X16">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
         <v>1.3</v>
@@ -2965,10 +2965,10 @@
         <v>3.75</v>
       </c>
       <c r="AD16">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE16">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF16">
         <v>1.82</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.32</v>
+        <v>1.73</v>
       </c>
       <c r="AK16">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3086,7 +3086,7 @@
         <v>3.6</v>
       </c>
       <c r="P17">
-        <v>4.42</v>
+        <v>4.33</v>
       </c>
       <c r="Q17">
         <v>2.32</v>
@@ -3098,13 +3098,13 @@
         <v>1.33</v>
       </c>
       <c r="T17">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="U17">
         <v>2.6</v>
       </c>
       <c r="V17">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W17">
         <v>1.06</v>
@@ -3113,16 +3113,16 @@
         <v>1</v>
       </c>
       <c r="Y17">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z17">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="AA17">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AB17">
-        <v>2.02</v>
+        <v>1.81</v>
       </c>
       <c r="AC17">
         <v>3.12</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AK17">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3415,10 +3415,10 @@
         <v>1.6</v>
       </c>
       <c r="Q19">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="R19">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="S19">
         <v>1.4</v>
@@ -3433,7 +3433,7 @@
         <v>1.36</v>
       </c>
       <c r="W19">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
         <v>1.04</v>
@@ -3460,10 +3460,10 @@
         <v>1.04</v>
       </c>
       <c r="AF19">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AG19">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>2.1</v>
       </c>
       <c r="AK19">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AL19">
         <v>0</v>

--- a/jogos_2026-07-29.xlsx
+++ b/jogos_2026-07-29.xlsx
@@ -2111,10 +2111,10 @@
         <v>4.89</v>
       </c>
       <c r="Q11">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="R11">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S11">
         <v>1.4</v>
@@ -2289,10 +2289,10 @@
         <v>2.81</v>
       </c>
       <c r="V12">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W12">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X12">
         <v>1.06</v>
@@ -2956,10 +2956,10 @@
         <v>2.99</v>
       </c>
       <c r="AA16">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AB16">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="AC16">
         <v>3.75</v>
@@ -2990,7 +2990,7 @@
         <v>1.73</v>
       </c>
       <c r="AK16">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3119,10 +3119,10 @@
         <v>3.4</v>
       </c>
       <c r="AA17">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AB17">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC17">
         <v>3.12</v>
@@ -3415,16 +3415,16 @@
         <v>1.6</v>
       </c>
       <c r="Q19">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="R19">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="S19">
         <v>1.4</v>
       </c>
       <c r="T19">
-        <v>2.88</v>
+        <v>2.71</v>
       </c>
       <c r="U19">
         <v>2.8</v>
@@ -3439,10 +3439,10 @@
         <v>1.04</v>
       </c>
       <c r="Y19">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="Z19">
-        <v>3.04</v>
+        <v>2.6</v>
       </c>
       <c r="AA19">
         <v>1.96</v>
@@ -3454,10 +3454,10 @@
         <v>3.34</v>
       </c>
       <c r="AD19">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE19">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF19">
         <v>1.91</v>
@@ -3479,7 +3479,7 @@
         <v>2.1</v>
       </c>
       <c r="AK19">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AL19">
         <v>0</v>

--- a/jogos_2026-07-29.xlsx
+++ b/jogos_2026-07-29.xlsx
@@ -2111,40 +2111,40 @@
         <v>4.89</v>
       </c>
       <c r="Q11">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="R11">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="S11">
         <v>1.4</v>
       </c>
       <c r="T11">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="U11">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="V11">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
         <v>1.33</v>
       </c>
       <c r="Z11">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="AA11">
         <v>2.1</v>
       </c>
       <c r="AB11">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC11">
         <v>3.9</v>
@@ -2159,7 +2159,7 @@
         <v>1.97</v>
       </c>
       <c r="AG11">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2274,10 +2274,10 @@
         <v>2.11</v>
       </c>
       <c r="Q12">
-        <v>4.1</v>
+        <v>3.94</v>
       </c>
       <c r="R12">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="S12">
         <v>1.38</v>
@@ -2286,31 +2286,31 @@
         <v>2.81</v>
       </c>
       <c r="U12">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="V12">
         <v>1.38</v>
       </c>
       <c r="W12">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
         <v>1.06</v>
       </c>
       <c r="Y12">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z12">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="AA12">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB12">
         <v>1.83</v>
       </c>
       <c r="AC12">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="AD12">
         <v>1.3</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AK12">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>3.45</v>
       </c>
       <c r="Q13">
-        <v>2.48</v>
+        <v>2.71</v>
       </c>
       <c r="R13">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="S13">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="T13">
         <v>2.56</v>
@@ -2455,28 +2455,28 @@
         <v>1.3</v>
       </c>
       <c r="W13">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X13">
         <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z13">
         <v>2.83</v>
       </c>
       <c r="AA13">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AB13">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AC13">
-        <v>4.01</v>
+        <v>3.3</v>
       </c>
       <c r="AD13">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE13">
         <v>1.02</v>
@@ -2485,7 +2485,7 @@
         <v>1.88</v>
       </c>
       <c r="AG13">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>1.27</v>
       </c>
       <c r="AK13">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2594,22 +2594,22 @@
         <v>1.33</v>
       </c>
       <c r="O14">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="P14">
-        <v>6.55</v>
+        <v>6.78</v>
       </c>
       <c r="Q14">
         <v>1.75</v>
       </c>
       <c r="R14">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="S14">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T14">
-        <v>3.92</v>
+        <v>3.75</v>
       </c>
       <c r="U14">
         <v>2.1</v>
@@ -2618,7 +2618,7 @@
         <v>1.67</v>
       </c>
       <c r="W14">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X14">
         <v>1.02</v>
@@ -2630,25 +2630,25 @@
         <v>5.44</v>
       </c>
       <c r="AA14">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AB14">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AC14">
         <v>2.23</v>
       </c>
       <c r="AD14">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE14">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AF14">
         <v>1.64</v>
       </c>
       <c r="AG14">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2917,19 +2917,19 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.75</v>
+        <v>3.66</v>
       </c>
       <c r="O16">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="Q16">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="R16">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="S16">
         <v>1.36</v>
@@ -2956,10 +2956,10 @@
         <v>2.99</v>
       </c>
       <c r="AA16">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB16">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AC16">
         <v>3.75</v>
@@ -2968,7 +2968,7 @@
         <v>1.22</v>
       </c>
       <c r="AE16">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF16">
         <v>1.82</v>
@@ -3086,16 +3086,16 @@
         <v>3.6</v>
       </c>
       <c r="P17">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="Q17">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="R17">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S17">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T17">
         <v>3.05</v>
@@ -3104,7 +3104,7 @@
         <v>2.6</v>
       </c>
       <c r="V17">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="W17">
         <v>1.06</v>
@@ -3113,10 +3113,10 @@
         <v>1</v>
       </c>
       <c r="Y17">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z17">
-        <v>3.4</v>
+        <v>3.94</v>
       </c>
       <c r="AA17">
         <v>1.95</v>
@@ -3125,16 +3125,16 @@
         <v>1.85</v>
       </c>
       <c r="AC17">
-        <v>3.12</v>
+        <v>2.85</v>
       </c>
       <c r="AD17">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE17">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF17">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG17">
         <v>1.95</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3415,10 +3415,10 @@
         <v>1.6</v>
       </c>
       <c r="Q19">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="R19">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="S19">
         <v>1.4</v>
@@ -3427,22 +3427,22 @@
         <v>2.71</v>
       </c>
       <c r="U19">
-        <v>2.8</v>
+        <v>2.29</v>
       </c>
       <c r="V19">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="W19">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X19">
         <v>1.04</v>
       </c>
       <c r="Y19">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z19">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="AA19">
         <v>1.96</v>
@@ -3454,16 +3454,16 @@
         <v>3.34</v>
       </c>
       <c r="AD19">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AE19">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF19">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AG19">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AK19">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AL19">
         <v>0</v>

--- a/jogos_2026-07-29.xlsx
+++ b/jogos_2026-07-29.xlsx
@@ -2431,10 +2431,10 @@
         <v>2.04</v>
       </c>
       <c r="O13">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="P13">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="Q13">
         <v>2.71</v>
@@ -2449,10 +2449,10 @@
         <v>2.56</v>
       </c>
       <c r="U13">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="V13">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W13">
         <v>1.07</v>
@@ -2467,7 +2467,7 @@
         <v>2.83</v>
       </c>
       <c r="AA13">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AB13">
         <v>1.65</v>
@@ -2485,7 +2485,7 @@
         <v>1.88</v>
       </c>
       <c r="AG13">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AK13">
         <v>1.63</v>
@@ -2600,10 +2600,10 @@
         <v>6.78</v>
       </c>
       <c r="Q14">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="R14">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="S14">
         <v>1.22</v>
@@ -2612,10 +2612,10 @@
         <v>3.75</v>
       </c>
       <c r="U14">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V14">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W14">
         <v>1.17</v>
@@ -2627,10 +2627,10 @@
         <v>1.09</v>
       </c>
       <c r="Z14">
-        <v>5.44</v>
+        <v>5.4</v>
       </c>
       <c r="AA14">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AB14">
         <v>2.5</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3418,7 +3418,7 @@
         <v>5</v>
       </c>
       <c r="R19">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="S19">
         <v>1.4</v>
@@ -3430,19 +3430,19 @@
         <v>2.29</v>
       </c>
       <c r="V19">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="W19">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="Z19">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="AA19">
         <v>1.96</v>
@@ -3454,7 +3454,7 @@
         <v>3.34</v>
       </c>
       <c r="AD19">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE19">
         <v>1.04</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>2</v>
+        <v>1.08</v>
       </c>
       <c r="AK19">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AL19">
         <v>0</v>

--- a/jogos_2026-07-29.xlsx
+++ b/jogos_2026-07-29.xlsx
@@ -801,16 +801,16 @@
         <v>2.2</v>
       </c>
       <c r="O3">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="P3">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="Q3">
         <v>2.83</v>
       </c>
       <c r="R3">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S3">
         <v>1.41</v>
@@ -819,10 +819,10 @@
         <v>2.69</v>
       </c>
       <c r="U3">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="V3">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W3">
         <v>1.02</v>
@@ -834,7 +834,7 @@
         <v>1.37</v>
       </c>
       <c r="Z3">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="AA3">
         <v>2.15</v>
@@ -843,19 +843,19 @@
         <v>1.67</v>
       </c>
       <c r="AC3">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AD3">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE3">
         <v>1.07</v>
       </c>
       <c r="AF3">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG3">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -982,13 +982,13 @@
         <v>2.77</v>
       </c>
       <c r="U4">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="V4">
         <v>1.37</v>
       </c>
       <c r="W4">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
         <v>1</v>
@@ -997,7 +997,7 @@
         <v>1.26</v>
       </c>
       <c r="Z4">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="AA4">
         <v>1.97</v>
@@ -1006,7 +1006,7 @@
         <v>1.8</v>
       </c>
       <c r="AC4">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AD4">
         <v>1.25</v>
@@ -1015,7 +1015,7 @@
         <v>1.05</v>
       </c>
       <c r="AF4">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG4">
         <v>1.83</v>
@@ -1034,7 +1034,7 @@
         <v>1.14</v>
       </c>
       <c r="AK4">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1130,13 +1130,13 @@
         <v>3.9</v>
       </c>
       <c r="P5">
-        <v>3.75</v>
+        <v>3.68</v>
       </c>
       <c r="Q5">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="R5">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="S5">
         <v>1.33</v>
@@ -1145,13 +1145,13 @@
         <v>3.18</v>
       </c>
       <c r="U5">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
       <c r="V5">
         <v>1.46</v>
       </c>
       <c r="W5">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X5">
         <v>1.02</v>
@@ -1160,13 +1160,13 @@
         <v>1.18</v>
       </c>
       <c r="Z5">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="AA5">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB5">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AC5">
         <v>2.72</v>
@@ -1175,7 +1175,7 @@
         <v>1.36</v>
       </c>
       <c r="AE5">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF5">
         <v>1.73</v>
@@ -1290,31 +1290,31 @@
         <v>1.9</v>
       </c>
       <c r="O6">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P6">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Q6">
         <v>2.44</v>
       </c>
       <c r="R6">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="S6">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T6">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="U6">
-        <v>2.73</v>
+        <v>2.89</v>
       </c>
       <c r="V6">
         <v>1.36</v>
       </c>
       <c r="W6">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X6">
         <v>1</v>
@@ -1326,10 +1326,10 @@
         <v>3.23</v>
       </c>
       <c r="AA6">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AB6">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AC6">
         <v>3.6</v>
@@ -1338,7 +1338,7 @@
         <v>1.25</v>
       </c>
       <c r="AE6">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF6">
         <v>1.83</v>
@@ -1459,10 +1459,10 @@
         <v>4.6</v>
       </c>
       <c r="Q7">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="R7">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="S7">
         <v>1.3</v>
@@ -1471,10 +1471,10 @@
         <v>3.3</v>
       </c>
       <c r="U7">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="V7">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W7">
         <v>1.09</v>
@@ -1486,19 +1486,19 @@
         <v>1.19</v>
       </c>
       <c r="Z7">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="AA7">
         <v>1.71</v>
       </c>
       <c r="AB7">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AC7">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="AD7">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AE7">
         <v>1.13</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK7">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1616,13 +1616,13 @@
         <v>6</v>
       </c>
       <c r="O8">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="P8">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="Q8">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="R8">
         <v>2.35</v>
@@ -1652,16 +1652,16 @@
         <v>3.76</v>
       </c>
       <c r="AA8">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AB8">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC8">
-        <v>2.85</v>
+        <v>2.72</v>
       </c>
       <c r="AD8">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE8">
         <v>1.11</v>
@@ -1670,7 +1670,7 @@
         <v>1.83</v>
       </c>
       <c r="AG8">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="O9">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="P9">
         <v>26</v>
@@ -1797,10 +1797,10 @@
         <v>5</v>
       </c>
       <c r="U9">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="V9">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="W9">
         <v>1.29</v>
@@ -1818,7 +1818,7 @@
         <v>1.23</v>
       </c>
       <c r="AB9">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="AC9">
         <v>1.7</v>
@@ -1827,13 +1827,13 @@
         <v>2.13</v>
       </c>
       <c r="AE9">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AF9">
         <v>2.45</v>
       </c>
       <c r="AG9">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1954,16 +1954,16 @@
         <v>2.39</v>
       </c>
       <c r="S10">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T10">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="U10">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V10">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W10">
         <v>1.09</v>
@@ -1975,7 +1975,7 @@
         <v>1.17</v>
       </c>
       <c r="Z10">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AA10">
         <v>1.6</v>
@@ -1987,13 +1987,13 @@
         <v>2.4</v>
       </c>
       <c r="AD10">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AE10">
         <v>1.14</v>
       </c>
       <c r="AF10">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG10">
         <v>1.83</v>
@@ -2111,55 +2111,55 @@
         <v>4.89</v>
       </c>
       <c r="Q11">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="R11">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S11">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T11">
         <v>2.9</v>
       </c>
       <c r="U11">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="V11">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W11">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
         <v>1.33</v>
       </c>
       <c r="Z11">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="AA11">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AB11">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC11">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="AD11">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE11">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF11">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="AG11">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK11">
         <v>2.15</v>
@@ -2274,43 +2274,43 @@
         <v>2.11</v>
       </c>
       <c r="Q12">
-        <v>3.94</v>
+        <v>4.25</v>
       </c>
       <c r="R12">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="S12">
         <v>1.38</v>
       </c>
       <c r="T12">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="U12">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="V12">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W12">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X12">
         <v>1.06</v>
       </c>
       <c r="Y12">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="AA12">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB12">
         <v>1.83</v>
       </c>
       <c r="AC12">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="AD12">
         <v>1.3</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AK12">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2763,55 +2763,55 @@
         <v>4.95</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,19 +2917,19 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.66</v>
+        <v>3.8</v>
       </c>
       <c r="O16">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P16">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="Q16">
-        <v>4.3</v>
+        <v>4.57</v>
       </c>
       <c r="R16">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="S16">
         <v>1.36</v>
@@ -2938,7 +2938,7 @@
         <v>2.88</v>
       </c>
       <c r="U16">
-        <v>2.94</v>
+        <v>3.12</v>
       </c>
       <c r="V16">
         <v>1.35</v>
@@ -2947,13 +2947,13 @@
         <v>1.05</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z16">
-        <v>2.99</v>
+        <v>3.24</v>
       </c>
       <c r="AA16">
         <v>2.1</v>
@@ -2962,10 +2962,10 @@
         <v>1.72</v>
       </c>
       <c r="AC16">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="AD16">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE16">
         <v>1.04</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.73</v>
+        <v>1.3</v>
       </c>
       <c r="AK16">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3083,10 +3083,10 @@
         <v>1.8</v>
       </c>
       <c r="O17">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P17">
-        <v>4.5</v>
+        <v>4.46</v>
       </c>
       <c r="Q17">
         <v>2.33</v>
@@ -3095,7 +3095,7 @@
         <v>2.2</v>
       </c>
       <c r="S17">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="T17">
         <v>3.05</v>
@@ -3104,7 +3104,7 @@
         <v>2.6</v>
       </c>
       <c r="V17">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W17">
         <v>1.06</v>
@@ -3119,7 +3119,7 @@
         <v>3.94</v>
       </c>
       <c r="AA17">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AB17">
         <v>1.85</v>

--- a/jogos_2026-07-29.xlsx
+++ b/jogos_2026-07-29.xlsx
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="O16">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P16">
-        <v>2.05</v>
+        <v>4.46</v>
       </c>
       <c r="Q16">
-        <v>4.57</v>
+        <v>2.33</v>
       </c>
       <c r="R16">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S16">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T16">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="U16">
-        <v>3.12</v>
+        <v>2.6</v>
       </c>
       <c r="V16">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W16">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X16">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y16">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="Z16">
-        <v>3.24</v>
+        <v>3.94</v>
       </c>
       <c r="AA16">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AB16">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AC16">
-        <v>3.74</v>
+        <v>2.85</v>
       </c>
       <c r="AD16">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE16">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF16">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AG16">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.25</v>
+        <v>1.93</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,65 +3080,65 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="O17">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P17">
-        <v>4.46</v>
+        <v>2.05</v>
       </c>
       <c r="Q17">
-        <v>2.33</v>
+        <v>4.57</v>
       </c>
       <c r="R17">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S17">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T17">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="U17">
-        <v>2.6</v>
+        <v>3.12</v>
       </c>
       <c r="V17">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W17">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X17">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="Z17">
-        <v>3.94</v>
+        <v>3.24</v>
       </c>
       <c r="AA17">
+        <v>2.1</v>
+      </c>
+      <c r="AB17">
+        <v>1.72</v>
+      </c>
+      <c r="AC17">
+        <v>3.74</v>
+      </c>
+      <c r="AD17">
+        <v>1.27</v>
+      </c>
+      <c r="AE17">
+        <v>1.04</v>
+      </c>
+      <c r="AF17">
         <v>1.82</v>
       </c>
-      <c r="AB17">
+      <c r="AG17">
         <v>1.85</v>
       </c>
-      <c r="AC17">
-        <v>2.85</v>
-      </c>
-      <c r="AD17">
-        <v>1.33</v>
-      </c>
-      <c r="AE17">
-        <v>1.08</v>
-      </c>
-      <c r="AF17">
-        <v>1.73</v>
-      </c>
-      <c r="AG17">
-        <v>1.95</v>
-      </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
+        <v>1.3</v>
+      </c>
+      <c r="AK17">
         <v>1.25</v>
-      </c>
-      <c r="AK17">
-        <v>1.93</v>
       </c>
       <c r="AL17">
         <v>0</v>

--- a/jogos_2026-07-29.xlsx
+++ b/jogos_2026-07-29.xlsx
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="O11">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="P11">
-        <v>4.89</v>
+        <v>4.8</v>
       </c>
       <c r="Q11">
         <v>2.25</v>
@@ -2117,49 +2117,49 @@
         <v>2.15</v>
       </c>
       <c r="S11">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="T11">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="U11">
-        <v>2.96</v>
+        <v>2.81</v>
       </c>
       <c r="V11">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W11">
         <v>1.04</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z11">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="AA11">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AB11">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AC11">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="AD11">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE11">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF11">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AG11">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK11">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,52 +2265,52 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="O12">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P12">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="Q12">
-        <v>4.25</v>
+        <v>4.35</v>
       </c>
       <c r="R12">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="S12">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T12">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="U12">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="V12">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W12">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X12">
         <v>1.06</v>
       </c>
       <c r="Y12">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z12">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="AA12">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AB12">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC12">
-        <v>3.24</v>
+        <v>3.12</v>
       </c>
       <c r="AD12">
         <v>1.3</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.8</v>
+        <v>1.31</v>
       </c>
       <c r="AK12">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2920,10 +2920,10 @@
         <v>1.8</v>
       </c>
       <c r="O16">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="P16">
-        <v>4.46</v>
+        <v>3.95</v>
       </c>
       <c r="Q16">
         <v>2.33</v>
@@ -2932,49 +2932,49 @@
         <v>2.2</v>
       </c>
       <c r="S16">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T16">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="U16">
         <v>2.6</v>
       </c>
       <c r="V16">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W16">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X16">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z16">
-        <v>3.94</v>
+        <v>3.7</v>
       </c>
       <c r="AA16">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AB16">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC16">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AD16">
         <v>1.33</v>
       </c>
       <c r="AE16">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF16">
         <v>1.73</v>
       </c>
       <c r="AG16">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK16">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,34 +3080,34 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="O17">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P17">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q17">
-        <v>4.57</v>
+        <v>4.64</v>
       </c>
       <c r="R17">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="S17">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T17">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="U17">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="V17">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W17">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X17">
         <v>1.03</v>
@@ -3116,10 +3116,10 @@
         <v>1.35</v>
       </c>
       <c r="Z17">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="AA17">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AB17">
         <v>1.72</v>
@@ -3134,7 +3134,7 @@
         <v>1.04</v>
       </c>
       <c r="AF17">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG17">
         <v>1.85</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.3</v>
+        <v>1.73</v>
       </c>
       <c r="AK17">
         <v>1.25</v>

--- a/jogos_2026-07-29.xlsx
+++ b/jogos_2026-07-29.xlsx
@@ -801,19 +801,19 @@
         <v>2.2</v>
       </c>
       <c r="O3">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="P3">
-        <v>3.03</v>
+        <v>3.1</v>
       </c>
       <c r="Q3">
         <v>2.83</v>
       </c>
       <c r="R3">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="S3">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T3">
         <v>2.69</v>
@@ -822,10 +822,10 @@
         <v>2.82</v>
       </c>
       <c r="V3">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W3">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
         <v>1.01</v>
@@ -840,7 +840,7 @@
         <v>2.15</v>
       </c>
       <c r="AB3">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC3">
         <v>4</v>
@@ -852,10 +852,10 @@
         <v>1.07</v>
       </c>
       <c r="AF3">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG3">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.3</v>
       </c>
       <c r="AK3">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="O4">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P4">
-        <v>4.6</v>
+        <v>4.83</v>
       </c>
       <c r="Q4">
         <v>2.3</v>
@@ -976,19 +976,19 @@
         <v>2.15</v>
       </c>
       <c r="S4">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T4">
         <v>2.77</v>
       </c>
       <c r="U4">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="V4">
         <v>1.37</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
         <v>1</v>
@@ -1015,10 +1015,10 @@
         <v>1.05</v>
       </c>
       <c r="AF4">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG4">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK4">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1130,22 +1130,22 @@
         <v>3.9</v>
       </c>
       <c r="P5">
-        <v>3.68</v>
+        <v>4.33</v>
       </c>
       <c r="Q5">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="R5">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="S5">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T5">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="U5">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="V5">
         <v>1.46</v>
@@ -1175,13 +1175,13 @@
         <v>1.36</v>
       </c>
       <c r="AE5">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF5">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AG5">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AK5">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,49 +1287,49 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="O6">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P6">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="Q6">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="R6">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="S6">
         <v>1.39</v>
       </c>
       <c r="T6">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="U6">
-        <v>2.89</v>
+        <v>2.82</v>
       </c>
       <c r="V6">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W6">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z6">
-        <v>3.23</v>
+        <v>2.93</v>
       </c>
       <c r="AA6">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AB6">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC6">
         <v>3.6</v>
@@ -1338,7 +1338,7 @@
         <v>1.25</v>
       </c>
       <c r="AE6">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF6">
         <v>1.83</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1453,16 +1453,16 @@
         <v>1.61</v>
       </c>
       <c r="O7">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="P7">
         <v>4.6</v>
       </c>
       <c r="Q7">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R7">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S7">
         <v>1.3</v>
@@ -1471,43 +1471,43 @@
         <v>3.3</v>
       </c>
       <c r="U7">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="V7">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W7">
         <v>1.09</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z7">
         <v>3.85</v>
       </c>
       <c r="AA7">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB7">
         <v>2.1</v>
       </c>
       <c r="AC7">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="AD7">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE7">
         <v>1.13</v>
       </c>
       <c r="AF7">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG7">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AK7">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="N8">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="O8">
         <v>4.1</v>
@@ -1622,13 +1622,13 @@
         <v>1.43</v>
       </c>
       <c r="Q8">
-        <v>5.5</v>
+        <v>6.15</v>
       </c>
       <c r="R8">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="S8">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T8">
         <v>3.1</v>
@@ -1652,16 +1652,16 @@
         <v>3.76</v>
       </c>
       <c r="AA8">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB8">
         <v>2</v>
       </c>
       <c r="AC8">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="AD8">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE8">
         <v>1.11</v>
@@ -1670,7 +1670,7 @@
         <v>1.83</v>
       </c>
       <c r="AG8">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="O9">
-        <v>13.2</v>
+        <v>9.9</v>
       </c>
       <c r="P9">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="Q9">
         <v>1.25</v>
@@ -1797,13 +1797,13 @@
         <v>5</v>
       </c>
       <c r="U9">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="V9">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="W9">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X9">
         <v>1.01</v>
@@ -1812,28 +1812,28 @@
         <v>1.03</v>
       </c>
       <c r="Z9">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="AA9">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AB9">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="AC9">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AD9">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="AE9">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AF9">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="AG9">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AK9">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1942,10 +1942,10 @@
         <v>1.34</v>
       </c>
       <c r="O10">
-        <v>4.99</v>
+        <v>5.25</v>
       </c>
       <c r="P10">
-        <v>8.449999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="Q10">
         <v>1.78</v>
@@ -1957,10 +1957,10 @@
         <v>1.29</v>
       </c>
       <c r="T10">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U10">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="V10">
         <v>1.57</v>
@@ -1975,22 +1975,22 @@
         <v>1.17</v>
       </c>
       <c r="Z10">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA10">
         <v>1.6</v>
       </c>
       <c r="AB10">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AC10">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AD10">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AE10">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF10">
         <v>1.87</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="O13">
-        <v>3.14</v>
+        <v>3.03</v>
       </c>
       <c r="P13">
-        <v>3.44</v>
+        <v>3.03</v>
       </c>
       <c r="Q13">
         <v>2.71</v>
@@ -2446,37 +2446,37 @@
         <v>1.45</v>
       </c>
       <c r="T13">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="U13">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="V13">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W13">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X13">
         <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z13">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="AA13">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="AB13">
         <v>1.65</v>
       </c>
       <c r="AC13">
-        <v>3.3</v>
+        <v>3.92</v>
       </c>
       <c r="AD13">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE13">
         <v>1.02</v>
@@ -2485,7 +2485,7 @@
         <v>1.88</v>
       </c>
       <c r="AG13">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK13">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,19 +2591,19 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="O14">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="P14">
-        <v>6.78</v>
+        <v>5.7</v>
       </c>
       <c r="Q14">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="R14">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="S14">
         <v>1.22</v>
@@ -2612,40 +2612,40 @@
         <v>3.75</v>
       </c>
       <c r="U14">
-        <v>2.18</v>
+        <v>2.29</v>
       </c>
       <c r="V14">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="W14">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X14">
         <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z14">
-        <v>5.4</v>
+        <v>5.05</v>
       </c>
       <c r="AA14">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AB14">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AC14">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="AD14">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AE14">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AF14">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AG14">
         <v>2.1</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK14">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2763,10 +2763,10 @@
         <v>4.95</v>
       </c>
       <c r="Q15">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="R15">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="S15">
         <v>1.22</v>
@@ -2796,13 +2796,13 @@
         <v>1.44</v>
       </c>
       <c r="AB15">
-        <v>2.43</v>
+        <v>2.58</v>
       </c>
       <c r="AC15">
         <v>2.21</v>
       </c>
       <c r="AD15">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AE15">
         <v>1.23</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK15">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3252,10 +3252,10 @@
         <v>2.13</v>
       </c>
       <c r="Q18">
-        <v>3.15</v>
+        <v>3.62</v>
       </c>
       <c r="R18">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="S18">
         <v>1.36</v>
@@ -3264,10 +3264,10 @@
         <v>2.75</v>
       </c>
       <c r="U18">
-        <v>2.55</v>
+        <v>2.83</v>
       </c>
       <c r="V18">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="W18">
         <v>1.05</v>
@@ -3279,28 +3279,28 @@
         <v>1.27</v>
       </c>
       <c r="Z18">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AA18">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AB18">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AC18">
         <v>3.05</v>
       </c>
       <c r="AD18">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AE18">
         <v>1.08</v>
       </c>
       <c r="AF18">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AG18">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK18">
         <v>1.34</v>
@@ -3421,31 +3421,31 @@
         <v>2.18</v>
       </c>
       <c r="S19">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T19">
-        <v>2.71</v>
+        <v>2.23</v>
       </c>
       <c r="U19">
-        <v>2.29</v>
+        <v>2.8</v>
       </c>
       <c r="V19">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W19">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X19">
         <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="Z19">
-        <v>3.04</v>
+        <v>2.6</v>
       </c>
       <c r="AA19">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AB19">
         <v>1.74</v>
@@ -3457,7 +3457,7 @@
         <v>1.24</v>
       </c>
       <c r="AE19">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF19">
         <v>1.82</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.08</v>
+        <v>2.1</v>
       </c>
       <c r="AK19">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AL19">
         <v>0</v>

--- a/jogos_2026-07-29.xlsx
+++ b/jogos_2026-07-29.xlsx
@@ -2114,37 +2114,37 @@
         <v>2.25</v>
       </c>
       <c r="R11">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="S11">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T11">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="U11">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="V11">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W11">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
         <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z11">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="AA11">
         <v>1.97</v>
       </c>
       <c r="AB11">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AC11">
         <v>3.24</v>
@@ -2153,7 +2153,7 @@
         <v>1.26</v>
       </c>
       <c r="AE11">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF11">
         <v>1.97</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AK11">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,25 +2265,25 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O12">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P12">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q12">
-        <v>4.35</v>
+        <v>4</v>
       </c>
       <c r="R12">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="S12">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T12">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="U12">
         <v>2.62</v>
@@ -2292,7 +2292,7 @@
         <v>1.41</v>
       </c>
       <c r="W12">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X12">
         <v>1.06</v>
@@ -2313,32 +2313,32 @@
         <v>3.12</v>
       </c>
       <c r="AD12">
+        <v>1.33</v>
+      </c>
+      <c r="AE12">
+        <v>1.11</v>
+      </c>
+      <c r="AF12">
+        <v>1.74</v>
+      </c>
+      <c r="AG12">
+        <v>1.97</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12">
         <v>1.3</v>
       </c>
-      <c r="AE12">
-        <v>1.1</v>
-      </c>
-      <c r="AF12">
-        <v>1.73</v>
-      </c>
-      <c r="AG12">
-        <v>2</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12">
-        <v>1.31</v>
-      </c>
       <c r="AK12">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2917,16 +2917,16 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="O16">
-        <v>3.64</v>
+        <v>3.48</v>
       </c>
       <c r="P16">
-        <v>3.95</v>
+        <v>3.58</v>
       </c>
       <c r="Q16">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="R16">
         <v>2.2</v>
@@ -2935,13 +2935,13 @@
         <v>1.35</v>
       </c>
       <c r="T16">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="U16">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="V16">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W16">
         <v>1.07</v>
@@ -2950,28 +2950,28 @@
         <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z16">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="AA16">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AB16">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC16">
         <v>3</v>
       </c>
       <c r="AD16">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE16">
         <v>1.09</v>
       </c>
       <c r="AF16">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG16">
         <v>2.05</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AK16">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="O17">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P17">
         <v>2</v>
@@ -3095,49 +3095,49 @@
         <v>2.19</v>
       </c>
       <c r="S17">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T17">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="U17">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="V17">
         <v>1.34</v>
       </c>
       <c r="W17">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y17">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z17">
-        <v>3</v>
+        <v>3.23</v>
       </c>
       <c r="AA17">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="AB17">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AC17">
-        <v>3.74</v>
+        <v>3.9</v>
       </c>
       <c r="AD17">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE17">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF17">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG17">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.73</v>
+        <v>1.34</v>
       </c>
       <c r="AK17">
         <v>1.25</v>

--- a/jogos_2026-07-29.xlsx
+++ b/jogos_2026-07-29.xlsx
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,65 +2102,65 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.73</v>
+        <v>3.75</v>
       </c>
       <c r="O11">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P11">
-        <v>4.8</v>
+        <v>1.95</v>
       </c>
       <c r="Q11">
-        <v>2.25</v>
+        <v>4.1</v>
       </c>
       <c r="R11">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="S11">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T11">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="U11">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="V11">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W11">
+        <v>1.09</v>
+      </c>
+      <c r="X11">
         <v>1.05</v>
       </c>
-      <c r="X11">
-        <v>1.01</v>
-      </c>
       <c r="Y11">
+        <v>1.24</v>
+      </c>
+      <c r="Z11">
+        <v>3.38</v>
+      </c>
+      <c r="AA11">
+        <v>1.89</v>
+      </c>
+      <c r="AB11">
+        <v>1.85</v>
+      </c>
+      <c r="AC11">
+        <v>3.08</v>
+      </c>
+      <c r="AD11">
         <v>1.33</v>
-      </c>
-      <c r="Z11">
-        <v>3.2</v>
-      </c>
-      <c r="AA11">
-        <v>1.97</v>
-      </c>
-      <c r="AB11">
-        <v>1.84</v>
-      </c>
-      <c r="AC11">
-        <v>3.24</v>
-      </c>
-      <c r="AD11">
-        <v>1.26</v>
       </c>
       <c r="AE11">
         <v>1.11</v>
       </c>
       <c r="AF11">
+        <v>1.74</v>
+      </c>
+      <c r="AG11">
         <v>1.97</v>
       </c>
-      <c r="AG11">
-        <v>1.74</v>
-      </c>
       <c r="AH11" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>2.05</v>
+        <v>1.2</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,65 +2265,65 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.75</v>
+        <v>1.73</v>
       </c>
       <c r="O12">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P12">
-        <v>1.95</v>
+        <v>4.8</v>
       </c>
       <c r="Q12">
-        <v>4</v>
+        <v>2.25</v>
       </c>
       <c r="R12">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="S12">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T12">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="U12">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="V12">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W12">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X12">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="Z12">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="AA12">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AB12">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AC12">
-        <v>3.12</v>
+        <v>3.24</v>
       </c>
       <c r="AD12">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE12">
         <v>1.11</v>
       </c>
       <c r="AF12">
+        <v>1.97</v>
+      </c>
+      <c r="AG12">
         <v>1.74</v>
       </c>
-      <c r="AG12">
-        <v>1.97</v>
-      </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK12">
-        <v>1.25</v>
+        <v>2.05</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2763,55 +2763,55 @@
         <v>4.95</v>
       </c>
       <c r="Q15">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="R15">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="S15">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T15">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U15">
-        <v>2.11</v>
+        <v>1.84</v>
       </c>
       <c r="V15">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W15">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
         <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z15">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="AA15">
         <v>1.44</v>
       </c>
       <c r="AB15">
-        <v>2.58</v>
+        <v>2.43</v>
       </c>
       <c r="AC15">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="AD15">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AE15">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AF15">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="AG15">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK15">
-        <v>2.75</v>
+        <v>2.39</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3080,16 +3080,16 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="O17">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="P17">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q17">
-        <v>4.64</v>
+        <v>4.7</v>
       </c>
       <c r="R17">
         <v>2.19</v>
@@ -3116,7 +3116,7 @@
         <v>1.33</v>
       </c>
       <c r="Z17">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="AA17">
         <v>2.07</v>
@@ -3137,7 +3137,7 @@
         <v>1.82</v>
       </c>
       <c r="AG17">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3252,10 +3252,10 @@
         <v>2.13</v>
       </c>
       <c r="Q18">
-        <v>3.62</v>
+        <v>3.15</v>
       </c>
       <c r="R18">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="S18">
         <v>1.36</v>
@@ -3264,22 +3264,22 @@
         <v>2.75</v>
       </c>
       <c r="U18">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="V18">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W18">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X18">
         <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z18">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="AA18">
         <v>1.97</v>
@@ -3291,16 +3291,16 @@
         <v>3.05</v>
       </c>
       <c r="AD18">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AE18">
         <v>1.08</v>
       </c>
       <c r="AF18">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AG18">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3421,40 +3421,40 @@
         <v>2.18</v>
       </c>
       <c r="S19">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T19">
-        <v>2.23</v>
+        <v>2.7</v>
       </c>
       <c r="U19">
-        <v>2.8</v>
+        <v>2.28</v>
       </c>
       <c r="V19">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W19">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
         <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="Z19">
-        <v>2.6</v>
+        <v>3.04</v>
       </c>
       <c r="AA19">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AB19">
-        <v>1.74</v>
+        <v>1.59</v>
       </c>
       <c r="AC19">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="AD19">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE19">
         <v>1.08</v>
@@ -3463,7 +3463,7 @@
         <v>1.82</v>
       </c>
       <c r="AG19">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>2.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK19">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AL19">
         <v>0</v>

--- a/jogos_2026-07-29.xlsx
+++ b/jogos_2026-07-29.xlsx
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O3">
         <v>3.1</v>
       </c>
       <c r="P3">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="Q3">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="R3">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="S3">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T3">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="U3">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="V3">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W3">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X3">
         <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Z3">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="AA3">
         <v>2.15</v>
       </c>
       <c r="AB3">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC3">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AD3">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE3">
         <v>1.07</v>
       </c>
       <c r="AF3">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG3">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.3</v>
       </c>
       <c r="AK3">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -976,37 +976,37 @@
         <v>2.15</v>
       </c>
       <c r="S4">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T4">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="U4">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="V4">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W4">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="Z4">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="AA4">
         <v>1.97</v>
       </c>
       <c r="AB4">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AC4">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AD4">
         <v>1.25</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK4">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,49 +1124,49 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="O5">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P5">
-        <v>4.33</v>
+        <v>3.68</v>
       </c>
       <c r="Q5">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="R5">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="S5">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T5">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U5">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="V5">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W5">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y5">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z5">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AA5">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB5">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AC5">
         <v>2.72</v>
@@ -1175,13 +1175,13 @@
         <v>1.36</v>
       </c>
       <c r="AE5">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF5">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AG5">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK5">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,28 +1287,28 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="O6">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P6">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="Q6">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="R6">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="S6">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T6">
         <v>2.9</v>
       </c>
       <c r="U6">
-        <v>2.82</v>
+        <v>2.89</v>
       </c>
       <c r="V6">
         <v>1.4</v>
@@ -1323,22 +1323,22 @@
         <v>1.3</v>
       </c>
       <c r="Z6">
-        <v>2.93</v>
+        <v>3.1</v>
       </c>
       <c r="AA6">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AB6">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AC6">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="AD6">
         <v>1.25</v>
       </c>
       <c r="AE6">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF6">
         <v>1.83</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK6">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,19 +1450,19 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="O7">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="P7">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="Q7">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="R7">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S7">
         <v>1.3</v>
@@ -1471,10 +1471,10 @@
         <v>3.3</v>
       </c>
       <c r="U7">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="V7">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W7">
         <v>1.09</v>
@@ -1486,19 +1486,19 @@
         <v>1.18</v>
       </c>
       <c r="Z7">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AA7">
         <v>1.7</v>
       </c>
       <c r="AB7">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AC7">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="AD7">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE7">
         <v>1.13</v>
@@ -1507,7 +1507,7 @@
         <v>1.73</v>
       </c>
       <c r="AG7">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.13</v>
       </c>
       <c r="AK7">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,22 +1613,22 @@
         </is>
       </c>
       <c r="N8">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O8">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="P8">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="Q8">
-        <v>6.15</v>
+        <v>6</v>
       </c>
       <c r="R8">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="S8">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T8">
         <v>3.1</v>
@@ -1640,37 +1640,37 @@
         <v>1.48</v>
       </c>
       <c r="W8">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y8">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z8">
-        <v>3.76</v>
+        <v>4</v>
       </c>
       <c r="AA8">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AB8">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AC8">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AD8">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE8">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF8">
         <v>1.83</v>
       </c>
       <c r="AG8">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="O9">
-        <v>9.9</v>
+        <v>12.5</v>
       </c>
       <c r="P9">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="Q9">
         <v>1.25</v>
@@ -1797,10 +1797,10 @@
         <v>5</v>
       </c>
       <c r="U9">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="V9">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="W9">
         <v>1.3</v>
@@ -1812,25 +1812,25 @@
         <v>1.03</v>
       </c>
       <c r="Z9">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="AA9">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AB9">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AC9">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AD9">
-        <v>2.16</v>
+        <v>1.96</v>
       </c>
       <c r="AE9">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AF9">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AG9">
         <v>1.48</v>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AK9">
         <v>8</v>
@@ -1939,31 +1939,31 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="O10">
-        <v>5.25</v>
+        <v>4.65</v>
       </c>
       <c r="P10">
-        <v>7.5</v>
+        <v>6.6</v>
       </c>
       <c r="Q10">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R10">
         <v>2.39</v>
       </c>
       <c r="S10">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T10">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="U10">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="V10">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="W10">
         <v>1.09</v>
@@ -1972,31 +1972,31 @@
         <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z10">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AA10">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AB10">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AC10">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AD10">
         <v>1.44</v>
       </c>
       <c r="AE10">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF10">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AG10">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>1.15</v>
       </c>
       <c r="AK10">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2775,10 +2775,10 @@
         <v>4</v>
       </c>
       <c r="U15">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V15">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W15">
         <v>1.11</v>
@@ -2787,10 +2787,10 @@
         <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z15">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA15">
         <v>1.44</v>
@@ -2799,10 +2799,10 @@
         <v>2.43</v>
       </c>
       <c r="AC15">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AD15">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE15">
         <v>1.28</v>
@@ -2827,7 +2827,7 @@
         <v>1.11</v>
       </c>
       <c r="AK15">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3445,7 +3445,7 @@
         <v>3.04</v>
       </c>
       <c r="AA19">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="AB19">
         <v>1.59</v>

--- a/jogos_2026-07-29.xlsx
+++ b/jogos_2026-07-29.xlsx
@@ -2123,16 +2123,16 @@
         <v>2.8</v>
       </c>
       <c r="U11">
-        <v>2.61</v>
+        <v>2.73</v>
       </c>
       <c r="V11">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W11">
         <v>1.09</v>
       </c>
       <c r="X11">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y11">
         <v>1.24</v>
@@ -2271,10 +2271,10 @@
         <v>3.7</v>
       </c>
       <c r="P12">
-        <v>4.8</v>
+        <v>4.55</v>
       </c>
       <c r="Q12">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="R12">
         <v>2.18</v>
@@ -2295,19 +2295,19 @@
         <v>1.05</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y12">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z12">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA12">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AB12">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AC12">
         <v>3.24</v>
@@ -2316,13 +2316,13 @@
         <v>1.26</v>
       </c>
       <c r="AE12">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF12">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="AG12">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2431,49 +2431,49 @@
         <v>1.93</v>
       </c>
       <c r="O13">
-        <v>3.03</v>
+        <v>3.35</v>
       </c>
       <c r="P13">
-        <v>3.03</v>
+        <v>3.9</v>
       </c>
       <c r="Q13">
-        <v>2.71</v>
+        <v>2.48</v>
       </c>
       <c r="R13">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="S13">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="T13">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="U13">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="V13">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W13">
+        <v>1.02</v>
+      </c>
+      <c r="X13">
         <v>1.01</v>
       </c>
-      <c r="X13">
-        <v>1.02</v>
-      </c>
       <c r="Y13">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z13">
         <v>3.05</v>
       </c>
       <c r="AA13">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AB13">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC13">
-        <v>3.92</v>
+        <v>3.3</v>
       </c>
       <c r="AD13">
         <v>1.18</v>
@@ -2482,10 +2482,10 @@
         <v>1.02</v>
       </c>
       <c r="AF13">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AG13">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK13">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,34 +2591,34 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="O14">
-        <v>4.55</v>
+        <v>4.85</v>
       </c>
       <c r="P14">
-        <v>5.7</v>
+        <v>6.45</v>
       </c>
       <c r="Q14">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="R14">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="S14">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T14">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="U14">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="V14">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="W14">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X14">
         <v>1.02</v>
@@ -2633,10 +2633,10 @@
         <v>1.46</v>
       </c>
       <c r="AB14">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="AC14">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="AD14">
         <v>1.56</v>
@@ -2648,7 +2648,7 @@
         <v>1.68</v>
       </c>
       <c r="AG14">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK14">
         <v>2.8</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="O16">
-        <v>3.48</v>
+        <v>3.75</v>
       </c>
       <c r="P16">
-        <v>3.58</v>
+        <v>4.2</v>
       </c>
       <c r="Q16">
         <v>2.2</v>
@@ -2932,10 +2932,10 @@
         <v>2.2</v>
       </c>
       <c r="S16">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T16">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="U16">
         <v>2.63</v>
@@ -2950,28 +2950,28 @@
         <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z16">
-        <v>3.62</v>
+        <v>3.54</v>
       </c>
       <c r="AA16">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AB16">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC16">
         <v>3</v>
       </c>
       <c r="AD16">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE16">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF16">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG16">
         <v>2.05</v>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK16">
         <v>1.95</v>
@@ -3080,19 +3080,19 @@
         </is>
       </c>
       <c r="N17">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="O17">
         <v>3.15</v>
       </c>
       <c r="P17">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q17">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="R17">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="S17">
         <v>1.36</v>
@@ -3101,7 +3101,7 @@
         <v>2.55</v>
       </c>
       <c r="U17">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="V17">
         <v>1.34</v>
@@ -3110,10 +3110,10 @@
         <v>1.05</v>
       </c>
       <c r="X17">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z17">
         <v>3.24</v>
@@ -3122,16 +3122,16 @@
         <v>2.07</v>
       </c>
       <c r="AB17">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AC17">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AD17">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE17">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF17">
         <v>1.82</v>

--- a/jogos_2026-07-29.xlsx
+++ b/jogos_2026-07-29.xlsx
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.77</v>
+        <v>4.25</v>
       </c>
       <c r="O16">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="P16">
+        <v>2</v>
+      </c>
+      <c r="Q16">
         <v>4.2</v>
       </c>
-      <c r="Q16">
-        <v>2.2</v>
-      </c>
       <c r="R16">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S16">
         <v>1.36</v>
       </c>
       <c r="T16">
-        <v>3.05</v>
+        <v>2.55</v>
       </c>
       <c r="U16">
-        <v>2.63</v>
+        <v>2.82</v>
       </c>
       <c r="V16">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="W16">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="Z16">
-        <v>3.54</v>
+        <v>3.24</v>
       </c>
       <c r="AA16">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="AB16">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AC16">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="AD16">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AE16">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF16">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AG16">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="AK16">
-        <v>1.95</v>
+        <v>1.25</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>4.25</v>
+        <v>1.77</v>
       </c>
       <c r="O17">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="P17">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="Q17">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="R17">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S17">
         <v>1.36</v>
       </c>
       <c r="T17">
-        <v>2.55</v>
+        <v>3.05</v>
       </c>
       <c r="U17">
-        <v>2.82</v>
+        <v>2.63</v>
       </c>
       <c r="V17">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="W17">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="Z17">
-        <v>3.24</v>
+        <v>3.54</v>
       </c>
       <c r="AA17">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="AB17">
+        <v>2</v>
+      </c>
+      <c r="AC17">
+        <v>3</v>
+      </c>
+      <c r="AD17">
+        <v>1.33</v>
+      </c>
+      <c r="AE17">
+        <v>1.13</v>
+      </c>
+      <c r="AF17">
         <v>1.72</v>
       </c>
-      <c r="AC17">
-        <v>3.75</v>
-      </c>
-      <c r="AD17">
-        <v>1.23</v>
-      </c>
-      <c r="AE17">
-        <v>1.05</v>
-      </c>
-      <c r="AF17">
-        <v>1.82</v>
-      </c>
       <c r="AG17">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AK17">
-        <v>1.25</v>
+        <v>1.95</v>
       </c>
       <c r="AL17">
         <v>0</v>

--- a/jogos_2026-07-29.xlsx
+++ b/jogos_2026-07-29.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL2">
         <v>0</v>

--- a/jogos_2026-07-29.xlsx
+++ b/jogos_2026-07-29.xlsx
@@ -638,16 +638,16 @@
         <v>1.85</v>
       </c>
       <c r="O2">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P2">
-        <v>3.95</v>
+        <v>3.82</v>
       </c>
       <c r="Q2">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="R2">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="S2">
         <v>1.41</v>
@@ -668,22 +668,22 @@
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Z2">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="AA2">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="AB2">
         <v>1.76</v>
       </c>
       <c r="AC2">
-        <v>3.31</v>
+        <v>3.5</v>
       </c>
       <c r="AD2">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE2">
         <v>1.05</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK2">
         <v>1.85</v>
@@ -798,19 +798,19 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="O3">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P3">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="Q3">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="R3">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="S3">
         <v>1.42</v>
@@ -825,7 +825,7 @@
         <v>1.35</v>
       </c>
       <c r="W3">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
         <v>1.01</v>
@@ -840,10 +840,10 @@
         <v>2.15</v>
       </c>
       <c r="AB3">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC3">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AD3">
         <v>1.22</v>
@@ -852,10 +852,10 @@
         <v>1.07</v>
       </c>
       <c r="AF3">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG3">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="O4">
         <v>3.45</v>
       </c>
       <c r="P4">
-        <v>4.83</v>
+        <v>4.55</v>
       </c>
       <c r="Q4">
         <v>2.3</v>
@@ -982,19 +982,19 @@
         <v>2.88</v>
       </c>
       <c r="U4">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V4">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W4">
         <v>1.08</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="Z4">
         <v>3.4</v>
@@ -1003,7 +1003,7 @@
         <v>1.97</v>
       </c>
       <c r="AB4">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC4">
         <v>3.3</v>
@@ -1012,13 +1012,13 @@
         <v>1.25</v>
       </c>
       <c r="AE4">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF4">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG4">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AK4">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,55 +1124,55 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="O5">
         <v>3.6</v>
       </c>
       <c r="P5">
-        <v>3.68</v>
+        <v>4.3</v>
       </c>
       <c r="Q5">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="R5">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="S5">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T5">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="U5">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="V5">
         <v>1.47</v>
       </c>
       <c r="W5">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X5">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z5">
         <v>3.85</v>
       </c>
       <c r="AA5">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AB5">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AC5">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="AD5">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE5">
         <v>1.1</v>
@@ -1181,7 +1181,7 @@
         <v>1.67</v>
       </c>
       <c r="AG5">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="O6">
         <v>3.4</v>
@@ -1302,49 +1302,49 @@
         <v>2.18</v>
       </c>
       <c r="S6">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T6">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="U6">
         <v>2.89</v>
       </c>
       <c r="V6">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X6">
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z6">
-        <v>3.1</v>
+        <v>3.23</v>
       </c>
       <c r="AA6">
         <v>2</v>
       </c>
       <c r="AB6">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AC6">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="AD6">
         <v>1.25</v>
       </c>
       <c r="AE6">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AF6">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG6">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="O7">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="P7">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="Q7">
         <v>2.05</v>
@@ -1471,7 +1471,7 @@
         <v>3.3</v>
       </c>
       <c r="U7">
-        <v>2.43</v>
+        <v>2.63</v>
       </c>
       <c r="V7">
         <v>1.44</v>
@@ -1483,19 +1483,19 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z7">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="AA7">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AB7">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AC7">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="AD7">
         <v>1.38</v>
@@ -1507,7 +1507,7 @@
         <v>1.73</v>
       </c>
       <c r="AG7">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.13</v>
       </c>
       <c r="AK7">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,22 +1613,22 @@
         </is>
       </c>
       <c r="N8">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="O8">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="P8">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Q8">
         <v>6</v>
       </c>
       <c r="R8">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="S8">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T8">
         <v>3.1</v>
@@ -1640,28 +1640,28 @@
         <v>1.48</v>
       </c>
       <c r="W8">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X8">
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z8">
         <v>4</v>
       </c>
       <c r="AA8">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB8">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AC8">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="AD8">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE8">
         <v>1.15</v>
@@ -1670,7 +1670,7 @@
         <v>1.83</v>
       </c>
       <c r="AG8">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="O9">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="P9">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Q9">
         <v>1.25</v>
@@ -1800,16 +1800,16 @@
         <v>1.7</v>
       </c>
       <c r="V9">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="W9">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y9">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Z9">
         <v>6.5</v>
@@ -1818,22 +1818,22 @@
         <v>1.25</v>
       </c>
       <c r="AB9">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AC9">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AD9">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AE9">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AF9">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AG9">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>1.04</v>
       </c>
       <c r="AK9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1942,43 +1942,43 @@
         <v>1.32</v>
       </c>
       <c r="O10">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="P10">
-        <v>6.6</v>
+        <v>8.75</v>
       </c>
       <c r="Q10">
         <v>1.76</v>
       </c>
       <c r="R10">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="S10">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T10">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U10">
         <v>2.23</v>
       </c>
       <c r="V10">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="W10">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
         <v>1.14</v>
       </c>
       <c r="Z10">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AA10">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AB10">
         <v>2.26</v>
@@ -2111,19 +2111,19 @@
         <v>1.95</v>
       </c>
       <c r="Q11">
-        <v>4.1</v>
+        <v>4.61</v>
       </c>
       <c r="R11">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="S11">
         <v>1.38</v>
       </c>
       <c r="T11">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="U11">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="V11">
         <v>1.42</v>
@@ -2156,10 +2156,10 @@
         <v>1.11</v>
       </c>
       <c r="AF11">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AG11">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK11">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2268,37 +2268,37 @@
         <v>1.73</v>
       </c>
       <c r="O12">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P12">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
       <c r="Q12">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="R12">
-        <v>2.18</v>
+        <v>2.29</v>
       </c>
       <c r="S12">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T12">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U12">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="V12">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W12">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
         <v>1.04</v>
       </c>
       <c r="Y12">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z12">
         <v>3.4</v>
@@ -2307,22 +2307,22 @@
         <v>1.95</v>
       </c>
       <c r="AB12">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AC12">
         <v>3.24</v>
       </c>
       <c r="AD12">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AE12">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF12">
         <v>1.86</v>
       </c>
       <c r="AG12">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK12">
         <v>2.05</v>
@@ -2428,34 +2428,34 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="O13">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P13">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="Q13">
-        <v>2.48</v>
+        <v>2.59</v>
       </c>
       <c r="R13">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="S13">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T13">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="U13">
         <v>2.88</v>
       </c>
       <c r="V13">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X13">
         <v>1.01</v>
@@ -2464,22 +2464,22 @@
         <v>1.29</v>
       </c>
       <c r="Z13">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="AA13">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB13">
         <v>1.67</v>
       </c>
       <c r="AC13">
-        <v>3.3</v>
+        <v>3.88</v>
       </c>
       <c r="AD13">
         <v>1.18</v>
       </c>
       <c r="AE13">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF13">
         <v>1.91</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK13">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,31 +2591,31 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="O14">
-        <v>4.85</v>
+        <v>4.5</v>
       </c>
       <c r="P14">
-        <v>6.45</v>
+        <v>5.91</v>
       </c>
       <c r="Q14">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="R14">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="S14">
         <v>1.25</v>
       </c>
       <c r="T14">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="U14">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="V14">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W14">
         <v>1.11</v>
@@ -2624,31 +2624,31 @@
         <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z14">
-        <v>5.05</v>
+        <v>4.95</v>
       </c>
       <c r="AA14">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AB14">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="AC14">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AD14">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AE14">
         <v>1.21</v>
       </c>
       <c r="AF14">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG14">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AK14">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="O15">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="P15">
-        <v>4.95</v>
+        <v>4.5</v>
       </c>
       <c r="Q15">
         <v>1.91</v>
@@ -2775,10 +2775,10 @@
         <v>4</v>
       </c>
       <c r="U15">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="V15">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W15">
         <v>1.11</v>
@@ -2787,10 +2787,10 @@
         <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Z15">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="AA15">
         <v>1.44</v>
@@ -2799,16 +2799,16 @@
         <v>2.43</v>
       </c>
       <c r="AC15">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AD15">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE15">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AF15">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AG15">
         <v>2.2</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK15">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,16 +2917,16 @@
         </is>
       </c>
       <c r="N16">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="O16">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P16">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q16">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="R16">
         <v>2.1</v>
@@ -2935,34 +2935,34 @@
         <v>1.36</v>
       </c>
       <c r="T16">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="U16">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="V16">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="W16">
         <v>1.05</v>
       </c>
       <c r="X16">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
         <v>1.31</v>
       </c>
       <c r="Z16">
-        <v>3.24</v>
+        <v>2.94</v>
       </c>
       <c r="AA16">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AB16">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC16">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AD16">
         <v>1.23</v>
@@ -2971,10 +2971,10 @@
         <v>1.05</v>
       </c>
       <c r="AF16">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG16">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
         <v>1.25</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="O17">
-        <v>3.75</v>
+        <v>3.48</v>
       </c>
       <c r="P17">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q17">
         <v>2.2</v>
@@ -3095,7 +3095,7 @@
         <v>2.2</v>
       </c>
       <c r="S17">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T17">
         <v>3.05</v>
@@ -3104,19 +3104,19 @@
         <v>2.63</v>
       </c>
       <c r="V17">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W17">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z17">
-        <v>3.54</v>
+        <v>3.81</v>
       </c>
       <c r="AA17">
         <v>1.8</v>
@@ -3125,13 +3125,13 @@
         <v>2</v>
       </c>
       <c r="AC17">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AD17">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE17">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF17">
         <v>1.72</v>
@@ -3153,7 +3153,7 @@
         <v>1.18</v>
       </c>
       <c r="AK17">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="O18">
+        <v>3.2</v>
+      </c>
+      <c r="P18">
+        <v>2</v>
+      </c>
+      <c r="Q18">
+        <v>3.5</v>
+      </c>
+      <c r="R18">
+        <v>2.25</v>
+      </c>
+      <c r="S18">
+        <v>1.3</v>
+      </c>
+      <c r="T18">
         <v>3.1</v>
       </c>
-      <c r="P18">
-        <v>2.13</v>
-      </c>
-      <c r="Q18">
-        <v>3.15</v>
-      </c>
-      <c r="R18">
-        <v>2.18</v>
-      </c>
-      <c r="S18">
-        <v>1.36</v>
-      </c>
-      <c r="T18">
-        <v>2.75</v>
-      </c>
       <c r="U18">
+        <v>2.55</v>
+      </c>
+      <c r="V18">
+        <v>1.44</v>
+      </c>
+      <c r="W18">
+        <v>1.11</v>
+      </c>
+      <c r="X18">
+        <v>1.04</v>
+      </c>
+      <c r="Y18">
+        <v>1.32</v>
+      </c>
+      <c r="Z18">
+        <v>3.17</v>
+      </c>
+      <c r="AA18">
+        <v>1.75</v>
+      </c>
+      <c r="AB18">
+        <v>2.02</v>
+      </c>
+      <c r="AC18">
         <v>2.89</v>
       </c>
-      <c r="V18">
-        <v>1.36</v>
-      </c>
-      <c r="W18">
-        <v>1.06</v>
-      </c>
-      <c r="X18">
-        <v>1.02</v>
-      </c>
-      <c r="Y18">
-        <v>1.25</v>
-      </c>
-      <c r="Z18">
-        <v>3.3</v>
-      </c>
-      <c r="AA18">
-        <v>1.97</v>
-      </c>
-      <c r="AB18">
-        <v>1.73</v>
-      </c>
-      <c r="AC18">
-        <v>3.05</v>
-      </c>
       <c r="AD18">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AE18">
         <v>1.08</v>
       </c>
       <c r="AF18">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AG18">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK18">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,37 +3406,37 @@
         </is>
       </c>
       <c r="N19">
-        <v>5.03</v>
+        <v>3.7</v>
       </c>
       <c r="O19">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="P19">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="Q19">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="R19">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="S19">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T19">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="U19">
         <v>2.28</v>
       </c>
       <c r="V19">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="W19">
         <v>1.05</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y19">
         <v>1.34</v>
@@ -3445,7 +3445,7 @@
         <v>3.04</v>
       </c>
       <c r="AA19">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="AB19">
         <v>1.59</v>
@@ -3454,16 +3454,16 @@
         <v>3.15</v>
       </c>
       <c r="AD19">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE19">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF19">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AG19">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AK19">
         <v>1.14</v>

--- a/jogos_2026-07-29.xlsx
+++ b/jogos_2026-07-29.xlsx
@@ -798,34 +798,34 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="O3">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P3">
         <v>3</v>
       </c>
       <c r="Q3">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="R3">
         <v>1.97</v>
       </c>
       <c r="S3">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T3">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="U3">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="V3">
         <v>1.35</v>
       </c>
       <c r="W3">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X3">
         <v>1.01</v>
@@ -834,16 +834,16 @@
         <v>1.33</v>
       </c>
       <c r="Z3">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="AA3">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB3">
         <v>1.66</v>
       </c>
       <c r="AC3">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="AD3">
         <v>1.22</v>
@@ -855,7 +855,7 @@
         <v>1.86</v>
       </c>
       <c r="AG3">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="O4">
         <v>3.45</v>
       </c>
       <c r="P4">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="Q4">
         <v>2.3</v>
@@ -976,25 +976,25 @@
         <v>2.15</v>
       </c>
       <c r="S4">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T4">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U4">
         <v>2.88</v>
       </c>
       <c r="V4">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W4">
         <v>1.08</v>
       </c>
       <c r="X4">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z4">
         <v>3.4</v>
@@ -1003,7 +1003,7 @@
         <v>1.97</v>
       </c>
       <c r="AB4">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AC4">
         <v>3.3</v>
@@ -1012,7 +1012,7 @@
         <v>1.25</v>
       </c>
       <c r="AE4">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF4">
         <v>1.85</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AK4">
         <v>2.14</v>
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="O5">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="P5">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="Q5">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="R5">
         <v>2.41</v>
@@ -1142,7 +1142,7 @@
         <v>1.3</v>
       </c>
       <c r="T5">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="U5">
         <v>2.45</v>
@@ -1154,34 +1154,34 @@
         <v>1.07</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z5">
         <v>3.85</v>
       </c>
       <c r="AA5">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AB5">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="AC5">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="AD5">
         <v>1.37</v>
       </c>
       <c r="AE5">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF5">
         <v>1.67</v>
       </c>
       <c r="AG5">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK5">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1293,28 +1293,28 @@
         <v>3.4</v>
       </c>
       <c r="P6">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="Q6">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="R6">
         <v>2.18</v>
       </c>
       <c r="S6">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="T6">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="U6">
         <v>2.89</v>
       </c>
       <c r="V6">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W6">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
         <v>1</v>
@@ -1329,7 +1329,7 @@
         <v>2</v>
       </c>
       <c r="AB6">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC6">
         <v>3.38</v>
@@ -1341,7 +1341,7 @@
         <v>1.04</v>
       </c>
       <c r="AF6">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG6">
         <v>1.91</v>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK6">
         <v>1.8</v>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="O7">
         <v>3.98</v>
@@ -1459,7 +1459,7 @@
         <v>4.6</v>
       </c>
       <c r="Q7">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="R7">
         <v>2.25</v>
@@ -1471,10 +1471,10 @@
         <v>3.3</v>
       </c>
       <c r="U7">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="V7">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W7">
         <v>1.09</v>
@@ -1486,25 +1486,25 @@
         <v>1.2</v>
       </c>
       <c r="Z7">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="AA7">
         <v>1.69</v>
       </c>
       <c r="AB7">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AC7">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="AD7">
         <v>1.38</v>
       </c>
       <c r="AE7">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF7">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG7">
         <v>2.05</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK7">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>6.6</v>
+        <v>6.25</v>
       </c>
       <c r="O8">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="P8">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="Q8">
         <v>6</v>
@@ -1640,7 +1640,7 @@
         <v>1.48</v>
       </c>
       <c r="W8">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X8">
         <v>1</v>
@@ -1649,7 +1649,7 @@
         <v>1.19</v>
       </c>
       <c r="Z8">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AA8">
         <v>1.75</v>
@@ -1661,10 +1661,10 @@
         <v>2.72</v>
       </c>
       <c r="AD8">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE8">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF8">
         <v>1.83</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="O9">
         <v>13</v>
@@ -1800,7 +1800,7 @@
         <v>1.7</v>
       </c>
       <c r="V9">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="W9">
         <v>1.28</v>
@@ -1815,25 +1815,25 @@
         <v>6.5</v>
       </c>
       <c r="AA9">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AB9">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="AC9">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AD9">
         <v>1.94</v>
       </c>
       <c r="AE9">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="AF9">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="AG9">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AK9">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="O10">
         <v>5</v>
       </c>
       <c r="P10">
-        <v>8.75</v>
+        <v>7.3</v>
       </c>
       <c r="Q10">
         <v>1.76</v>
@@ -1960,10 +1960,10 @@
         <v>3.2</v>
       </c>
       <c r="U10">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="V10">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W10">
         <v>1.11</v>
@@ -1972,13 +1972,13 @@
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z10">
         <v>4.4</v>
       </c>
       <c r="AA10">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AB10">
         <v>2.26</v>
@@ -1987,7 +1987,7 @@
         <v>2.4</v>
       </c>
       <c r="AD10">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AE10">
         <v>1.14</v>

--- a/jogos_2026-07-29.xlsx
+++ b/jogos_2026-07-29.xlsx
@@ -641,25 +641,25 @@
         <v>3.05</v>
       </c>
       <c r="P2">
-        <v>3.82</v>
+        <v>3.95</v>
       </c>
       <c r="Q2">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="R2">
         <v>2.1</v>
       </c>
       <c r="S2">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T2">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="U2">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="V2">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W2">
         <v>1.06</v>
@@ -677,16 +677,16 @@
         <v>1.99</v>
       </c>
       <c r="AB2">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AC2">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AD2">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE2">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF2">
         <v>1.8</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK2">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -807,22 +807,22 @@
         <v>3</v>
       </c>
       <c r="Q3">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="R3">
-        <v>1.97</v>
+        <v>2.12</v>
       </c>
       <c r="S3">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="T3">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="U3">
         <v>3.1</v>
       </c>
       <c r="V3">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W3">
         <v>1.02</v>
@@ -831,22 +831,22 @@
         <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z3">
-        <v>2.95</v>
+        <v>2.72</v>
       </c>
       <c r="AA3">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AB3">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AC3">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AD3">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE3">
         <v>1.07</v>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="O4">
         <v>3.45</v>
@@ -979,13 +979,13 @@
         <v>1.35</v>
       </c>
       <c r="T4">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="U4">
         <v>2.88</v>
       </c>
       <c r="V4">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W4">
         <v>1.08</v>
@@ -1003,7 +1003,7 @@
         <v>1.97</v>
       </c>
       <c r="AB4">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AC4">
         <v>3.3</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK4">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,34 +1124,34 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="O5">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="P5">
-        <v>4.35</v>
+        <v>3.8</v>
       </c>
       <c r="Q5">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="R5">
-        <v>2.41</v>
+        <v>2.27</v>
       </c>
       <c r="S5">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T5">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="U5">
         <v>2.45</v>
       </c>
       <c r="V5">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="W5">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
         <v>1.01</v>
@@ -1160,25 +1160,25 @@
         <v>1.21</v>
       </c>
       <c r="Z5">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="AA5">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AB5">
-        <v>1.98</v>
+        <v>2.11</v>
       </c>
       <c r="AC5">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AD5">
         <v>1.37</v>
       </c>
       <c r="AE5">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF5">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AG5">
         <v>2</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AK5">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="O6">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P6">
-        <v>4.05</v>
+        <v>3.85</v>
       </c>
       <c r="Q6">
         <v>2.35</v>
@@ -1302,10 +1302,10 @@
         <v>2.18</v>
       </c>
       <c r="S6">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T6">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="U6">
         <v>2.89</v>
@@ -1323,28 +1323,28 @@
         <v>1.32</v>
       </c>
       <c r="Z6">
-        <v>3.23</v>
+        <v>3.1</v>
       </c>
       <c r="AA6">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB6">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC6">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="AD6">
         <v>1.25</v>
       </c>
       <c r="AE6">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF6">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG6">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK6">
         <v>1.8</v>
@@ -1450,19 +1450,19 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="O7">
-        <v>3.98</v>
+        <v>4.2</v>
       </c>
       <c r="P7">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="Q7">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="R7">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S7">
         <v>1.3</v>
@@ -1486,28 +1486,28 @@
         <v>1.2</v>
       </c>
       <c r="Z7">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="AA7">
         <v>1.69</v>
       </c>
       <c r="AB7">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AC7">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="AD7">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AE7">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF7">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG7">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.17</v>
       </c>
       <c r="AK7">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,25 +1613,25 @@
         </is>
       </c>
       <c r="N8">
-        <v>6.25</v>
+        <v>6.19</v>
       </c>
       <c r="O8">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="P8">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="Q8">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="R8">
         <v>2.48</v>
       </c>
       <c r="S8">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T8">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="U8">
         <v>2.45</v>
@@ -1643,19 +1643,19 @@
         <v>1.07</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y8">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z8">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AA8">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB8">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AC8">
         <v>2.72</v>
@@ -1664,7 +1664,7 @@
         <v>1.44</v>
       </c>
       <c r="AE8">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AF8">
         <v>1.83</v>
@@ -1800,28 +1800,28 @@
         <v>1.7</v>
       </c>
       <c r="V9">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="W9">
         <v>1.28</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
         <v>1.07</v>
       </c>
       <c r="Z9">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="AA9">
         <v>1.28</v>
       </c>
       <c r="AB9">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AC9">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AD9">
         <v>1.94</v>
@@ -1830,7 +1830,7 @@
         <v>1.41</v>
       </c>
       <c r="AF9">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="AG9">
         <v>1.36</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AK9">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="O10">
         <v>5</v>
       </c>
       <c r="P10">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="Q10">
         <v>1.76</v>
@@ -1954,31 +1954,31 @@
         <v>2.43</v>
       </c>
       <c r="S10">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T10">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="U10">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="V10">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W10">
         <v>1.11</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z10">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="AA10">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AB10">
         <v>2.26</v>
@@ -1987,16 +1987,16 @@
         <v>2.4</v>
       </c>
       <c r="AD10">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AE10">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF10">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AG10">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2108,46 +2108,46 @@
         <v>3.5</v>
       </c>
       <c r="P11">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Q11">
-        <v>4.61</v>
+        <v>4.8</v>
       </c>
       <c r="R11">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="S11">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T11">
-        <v>2.81</v>
+        <v>2.93</v>
       </c>
       <c r="U11">
         <v>2.7</v>
       </c>
       <c r="V11">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W11">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
         <v>1.06</v>
       </c>
       <c r="Y11">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z11">
-        <v>3.38</v>
+        <v>3.24</v>
       </c>
       <c r="AA11">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="AB11">
         <v>1.85</v>
       </c>
       <c r="AC11">
-        <v>3.08</v>
+        <v>3.24</v>
       </c>
       <c r="AD11">
         <v>1.33</v>
@@ -2156,10 +2156,10 @@
         <v>1.11</v>
       </c>
       <c r="AF11">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AG11">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.31</v>
+        <v>1.87</v>
       </c>
       <c r="AK11">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="O12">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P12">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="Q12">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="R12">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="S12">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T12">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U12">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="V12">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W12">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X12">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y12">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z12">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA12">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AB12">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AC12">
         <v>3.24</v>
       </c>
       <c r="AD12">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AE12">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF12">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG12">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK12">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,52 +2428,52 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="O13">
         <v>3.3</v>
       </c>
       <c r="P13">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="Q13">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="R13">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="S13">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T13">
-        <v>2.59</v>
+        <v>2.68</v>
       </c>
       <c r="U13">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V13">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W13">
         <v>1.01</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="Z13">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AA13">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AB13">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC13">
-        <v>3.88</v>
+        <v>3.92</v>
       </c>
       <c r="AD13">
         <v>1.18</v>
@@ -2482,10 +2482,10 @@
         <v>1.07</v>
       </c>
       <c r="AF13">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AG13">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK13">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2597,58 +2597,58 @@
         <v>4.5</v>
       </c>
       <c r="P14">
-        <v>5.91</v>
+        <v>5.5</v>
       </c>
       <c r="Q14">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="R14">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="S14">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="T14">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="U14">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="V14">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W14">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X14">
         <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z14">
-        <v>4.95</v>
+        <v>5.1</v>
       </c>
       <c r="AA14">
         <v>1.45</v>
       </c>
       <c r="AB14">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AC14">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="AD14">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AE14">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AF14">
         <v>1.67</v>
       </c>
       <c r="AG14">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AK14">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,34 +2754,34 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="O15">
-        <v>4.1</v>
+        <v>4.55</v>
       </c>
       <c r="P15">
         <v>4.5</v>
       </c>
       <c r="Q15">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="R15">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="S15">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T15">
         <v>4</v>
       </c>
       <c r="U15">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="V15">
         <v>1.65</v>
       </c>
       <c r="W15">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X15">
         <v>1.02</v>
@@ -2799,19 +2799,19 @@
         <v>2.43</v>
       </c>
       <c r="AC15">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AD15">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AE15">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF15">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG15">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AK15">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2920,37 +2920,37 @@
         <v>3.8</v>
       </c>
       <c r="O16">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P16">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q16">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="R16">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="S16">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T16">
         <v>2.57</v>
       </c>
       <c r="U16">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="V16">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W16">
         <v>1.05</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y16">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z16">
         <v>2.94</v>
@@ -2959,22 +2959,22 @@
         <v>2.13</v>
       </c>
       <c r="AB16">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC16">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AD16">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE16">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF16">
         <v>1.85</v>
       </c>
       <c r="AG16">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.25</v>
+        <v>1.87</v>
       </c>
       <c r="AK16">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,16 +3080,16 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="O17">
-        <v>3.48</v>
+        <v>3.8</v>
       </c>
       <c r="P17">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="Q17">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R17">
         <v>2.2</v>
@@ -3098,25 +3098,25 @@
         <v>1.35</v>
       </c>
       <c r="T17">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="U17">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="V17">
         <v>1.44</v>
       </c>
       <c r="W17">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X17">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y17">
         <v>1.21</v>
       </c>
       <c r="Z17">
-        <v>3.81</v>
+        <v>3.62</v>
       </c>
       <c r="AA17">
         <v>1.8</v>
@@ -3125,13 +3125,13 @@
         <v>2</v>
       </c>
       <c r="AC17">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="AD17">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE17">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF17">
         <v>1.72</v>
@@ -3153,7 +3153,7 @@
         <v>1.18</v>
       </c>
       <c r="AK17">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.75</v>
+        <v>3.14</v>
       </c>
       <c r="O18">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="P18">
         <v>2</v>
@@ -3255,19 +3255,19 @@
         <v>3.5</v>
       </c>
       <c r="R18">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S18">
         <v>1.3</v>
       </c>
       <c r="T18">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="U18">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="V18">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W18">
         <v>1.11</v>
@@ -3276,31 +3276,31 @@
         <v>1.04</v>
       </c>
       <c r="Y18">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Z18">
-        <v>3.17</v>
+        <v>3.65</v>
       </c>
       <c r="AA18">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AB18">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AC18">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="AD18">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AE18">
         <v>1.08</v>
       </c>
       <c r="AF18">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AG18">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.23</v>
+        <v>1.58</v>
       </c>
       <c r="AK18">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.7</v>
+        <v>4.68</v>
       </c>
       <c r="O19">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="P19">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q19">
-        <v>5.15</v>
+        <v>5.4</v>
       </c>
       <c r="R19">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="S19">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T19">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="U19">
-        <v>2.28</v>
+        <v>2.75</v>
       </c>
       <c r="V19">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="W19">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
         <v>1.34</v>
       </c>
       <c r="Z19">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AA19">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AB19">
-        <v>1.59</v>
+        <v>1.76</v>
       </c>
       <c r="AC19">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="AD19">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AE19">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF19">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG19">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="AK19">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AL19">
         <v>0</v>

--- a/jogos_2026-07-29.xlsx
+++ b/jogos_2026-07-29.xlsx
@@ -798,52 +798,52 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="O3">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P3">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="Q3">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="R3">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="S3">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="T3">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="U3">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="V3">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W3">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X3">
         <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z3">
-        <v>2.72</v>
+        <v>2.93</v>
       </c>
       <c r="AA3">
-        <v>2.09</v>
+        <v>2.21</v>
       </c>
       <c r="AB3">
         <v>1.6</v>
       </c>
       <c r="AC3">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="AD3">
         <v>1.23</v>
@@ -852,10 +852,10 @@
         <v>1.07</v>
       </c>
       <c r="AF3">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AG3">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK3">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -964,10 +964,10 @@
         <v>1.72</v>
       </c>
       <c r="O4">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>4.5</v>
+        <v>3.93</v>
       </c>
       <c r="Q4">
         <v>2.3</v>
@@ -979,10 +979,10 @@
         <v>1.35</v>
       </c>
       <c r="T4">
+        <v>2.9</v>
+      </c>
+      <c r="U4">
         <v>2.8</v>
-      </c>
-      <c r="U4">
-        <v>2.88</v>
       </c>
       <c r="V4">
         <v>1.39</v>
@@ -991,7 +991,7 @@
         <v>1.08</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
         <v>1.3</v>
@@ -1000,25 +1000,25 @@
         <v>3.4</v>
       </c>
       <c r="AA4">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AB4">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AC4">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AD4">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE4">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF4">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG4">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.24</v>
       </c>
       <c r="AK4">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,31 +1124,31 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="O5">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P5">
-        <v>3.8</v>
+        <v>4.63</v>
       </c>
       <c r="Q5">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="R5">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="S5">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T5">
         <v>3</v>
       </c>
       <c r="U5">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="V5">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W5">
         <v>1.08</v>
@@ -1160,10 +1160,10 @@
         <v>1.21</v>
       </c>
       <c r="Z5">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="AA5">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AB5">
         <v>2.11</v>
@@ -1175,7 +1175,7 @@
         <v>1.37</v>
       </c>
       <c r="AE5">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF5">
         <v>1.71</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AK5">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,28 +1287,28 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O6">
         <v>3.3</v>
       </c>
       <c r="P6">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="Q6">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="R6">
         <v>2.18</v>
       </c>
       <c r="S6">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T6">
         <v>2.8</v>
       </c>
       <c r="U6">
-        <v>2.89</v>
+        <v>2.99</v>
       </c>
       <c r="V6">
         <v>1.36</v>
@@ -1317,34 +1317,34 @@
         <v>1.08</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z6">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AA6">
         <v>2.1</v>
       </c>
       <c r="AB6">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AC6">
-        <v>3.44</v>
+        <v>3.62</v>
       </c>
       <c r="AD6">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE6">
         <v>1.08</v>
       </c>
       <c r="AF6">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AG6">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK6">
         <v>1.8</v>
@@ -1456,58 +1456,58 @@
         <v>4.2</v>
       </c>
       <c r="P7">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="Q7">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="R7">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S7">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T7">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U7">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V7">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W7">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X7">
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z7">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AA7">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AB7">
         <v>2.2</v>
       </c>
       <c r="AC7">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="AD7">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AE7">
         <v>1.18</v>
       </c>
       <c r="AF7">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG7">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="N8">
-        <v>6.19</v>
+        <v>5.5</v>
       </c>
       <c r="O8">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P8">
         <v>1.48</v>
@@ -1625,7 +1625,7 @@
         <v>6.5</v>
       </c>
       <c r="R8">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="S8">
         <v>1.35</v>
@@ -1664,7 +1664,7 @@
         <v>1.44</v>
       </c>
       <c r="AE8">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF8">
         <v>1.83</v>
@@ -1776,19 +1776,19 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="O9">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="P9">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q9">
         <v>1.25</v>
       </c>
       <c r="R9">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="S9">
         <v>1.15</v>
@@ -1797,13 +1797,13 @@
         <v>5</v>
       </c>
       <c r="U9">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="V9">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="W9">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X9">
         <v>1.01</v>
@@ -1818,7 +1818,7 @@
         <v>1.28</v>
       </c>
       <c r="AB9">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AC9">
         <v>1.7</v>
@@ -1830,7 +1830,7 @@
         <v>1.41</v>
       </c>
       <c r="AF9">
-        <v>2.64</v>
+        <v>2.85</v>
       </c>
       <c r="AG9">
         <v>1.36</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AK9">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1942,22 +1942,22 @@
         <v>1.31</v>
       </c>
       <c r="O10">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="P10">
-        <v>7.2</v>
+        <v>9.35</v>
       </c>
       <c r="Q10">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="R10">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="S10">
         <v>1.29</v>
       </c>
       <c r="T10">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U10">
         <v>2.25</v>
@@ -1978,25 +1978,25 @@
         <v>4.25</v>
       </c>
       <c r="AA10">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB10">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="AC10">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AD10">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AE10">
         <v>1.18</v>
       </c>
       <c r="AF10">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG10">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK10">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="AL10">
         <v>0</v>

--- a/jogos_2026-07-29.xlsx
+++ b/jogos_2026-07-29.xlsx
@@ -641,13 +641,13 @@
         <v>3.05</v>
       </c>
       <c r="P2">
-        <v>3.95</v>
+        <v>3.82</v>
       </c>
       <c r="Q2">
         <v>2.44</v>
       </c>
       <c r="R2">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S2">
         <v>1.36</v>
@@ -665,31 +665,31 @@
         <v>1.06</v>
       </c>
       <c r="X2">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y2">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z2">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="AA2">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AB2">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC2">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AD2">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE2">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF2">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG2">
         <v>1.91</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK2">
         <v>1.8</v>
@@ -801,22 +801,22 @@
         <v>2.15</v>
       </c>
       <c r="O3">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P3">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q3">
-        <v>2.78</v>
+        <v>2.73</v>
       </c>
       <c r="R3">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="S3">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T3">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="U3">
         <v>3.15</v>
@@ -831,31 +831,31 @@
         <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z3">
         <v>2.93</v>
       </c>
       <c r="AA3">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AB3">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC3">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AD3">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AE3">
         <v>1.07</v>
       </c>
       <c r="AF3">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AG3">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK3">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="O4">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P4">
-        <v>3.93</v>
+        <v>3.85</v>
       </c>
       <c r="Q4">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R4">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S4">
+        <v>1.45</v>
+      </c>
+      <c r="T4">
+        <v>2.61</v>
+      </c>
+      <c r="U4">
+        <v>3</v>
+      </c>
+      <c r="V4">
         <v>1.35</v>
       </c>
-      <c r="T4">
-        <v>2.9</v>
-      </c>
-      <c r="U4">
-        <v>2.8</v>
-      </c>
-      <c r="V4">
-        <v>1.39</v>
-      </c>
       <c r="W4">
+        <v>1.05</v>
+      </c>
+      <c r="X4">
+        <v>1.05</v>
+      </c>
+      <c r="Y4">
+        <v>1.33</v>
+      </c>
+      <c r="Z4">
+        <v>2.85</v>
+      </c>
+      <c r="AA4">
+        <v>2.18</v>
+      </c>
+      <c r="AB4">
+        <v>1.65</v>
+      </c>
+      <c r="AC4">
+        <v>3.85</v>
+      </c>
+      <c r="AD4">
+        <v>1.18</v>
+      </c>
+      <c r="AE4">
         <v>1.08</v>
       </c>
-      <c r="X4">
-        <v>1.04</v>
-      </c>
-      <c r="Y4">
-        <v>1.3</v>
-      </c>
-      <c r="Z4">
-        <v>3.4</v>
-      </c>
-      <c r="AA4">
-        <v>2</v>
-      </c>
-      <c r="AB4">
-        <v>1.77</v>
-      </c>
-      <c r="AC4">
-        <v>3.4</v>
-      </c>
-      <c r="AD4">
-        <v>1.3</v>
-      </c>
-      <c r="AE4">
-        <v>1.04</v>
-      </c>
       <c r="AF4">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="AG4">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK4">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,80 +1124,80 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="O5">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P5">
-        <v>4.63</v>
+        <v>4</v>
       </c>
       <c r="Q5">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="R5">
-        <v>2.21</v>
+        <v>2.26</v>
       </c>
       <c r="S5">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="T5">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U5">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="V5">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W5">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X5">
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="Z5">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="AA5">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AB5">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="AC5">
-        <v>2.88</v>
+        <v>2.39</v>
       </c>
       <c r="AD5">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="AE5">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF5">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AG5">
+        <v>2.26</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5">
+        <v>1.11</v>
+      </c>
+      <c r="AK5">
         <v>2</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5">
-        <v>1.26</v>
-      </c>
-      <c r="AK5">
-        <v>2.05</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1290,10 +1290,10 @@
         <v>1.9</v>
       </c>
       <c r="O6">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P6">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Q6">
         <v>2.37</v>
@@ -1302,49 +1302,49 @@
         <v>2.18</v>
       </c>
       <c r="S6">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T6">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="U6">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="V6">
         <v>1.36</v>
       </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y6">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z6">
         <v>3.15</v>
       </c>
       <c r="AA6">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB6">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC6">
-        <v>3.62</v>
+        <v>3.8</v>
       </c>
       <c r="AD6">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE6">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF6">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AG6">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AK6">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="O7">
         <v>4.2</v>
@@ -1459,52 +1459,52 @@
         <v>4.1</v>
       </c>
       <c r="Q7">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="R7">
         <v>2.45</v>
       </c>
       <c r="S7">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T7">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U7">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V7">
+        <v>1.52</v>
+      </c>
+      <c r="W7">
+        <v>1.12</v>
+      </c>
+      <c r="X7">
+        <v>1.03</v>
+      </c>
+      <c r="Y7">
+        <v>1.15</v>
+      </c>
+      <c r="Z7">
+        <v>4.5</v>
+      </c>
+      <c r="AA7">
+        <v>1.6</v>
+      </c>
+      <c r="AB7">
+        <v>2.25</v>
+      </c>
+      <c r="AC7">
+        <v>2.36</v>
+      </c>
+      <c r="AD7">
         <v>1.5</v>
-      </c>
-      <c r="W7">
-        <v>1.1</v>
-      </c>
-      <c r="X7">
-        <v>1</v>
-      </c>
-      <c r="Y7">
-        <v>1.17</v>
-      </c>
-      <c r="Z7">
-        <v>4.2</v>
-      </c>
-      <c r="AA7">
-        <v>1.67</v>
-      </c>
-      <c r="AB7">
-        <v>2.2</v>
-      </c>
-      <c r="AC7">
-        <v>2.44</v>
-      </c>
-      <c r="AD7">
-        <v>1.48</v>
       </c>
       <c r="AE7">
         <v>1.18</v>
       </c>
       <c r="AF7">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AG7">
         <v>2.02</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK7">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1616,22 +1616,22 @@
         <v>5.5</v>
       </c>
       <c r="O8">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P8">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Q8">
-        <v>6.5</v>
+        <v>5.65</v>
       </c>
       <c r="R8">
         <v>2.38</v>
       </c>
       <c r="S8">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T8">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="U8">
         <v>2.45</v>
@@ -1640,37 +1640,37 @@
         <v>1.48</v>
       </c>
       <c r="W8">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
         <v>1.05</v>
       </c>
       <c r="Y8">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z8">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AA8">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AB8">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AC8">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="AD8">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AE8">
         <v>1.11</v>
       </c>
       <c r="AF8">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG8">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK8">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,19 +1776,19 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="O9">
-        <v>15.5</v>
+        <v>9.9</v>
       </c>
       <c r="P9">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="Q9">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="R9">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="S9">
         <v>1.15</v>
@@ -1800,40 +1800,40 @@
         <v>1.78</v>
       </c>
       <c r="V9">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="W9">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y9">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Z9">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="AA9">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AB9">
-        <v>3.65</v>
+        <v>3.78</v>
       </c>
       <c r="AC9">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AD9">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AE9">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AF9">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
       <c r="AG9">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AK9">
         <v>9</v>
@@ -1939,31 +1939,31 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="O10">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="P10">
-        <v>9.35</v>
+        <v>7.1</v>
       </c>
       <c r="Q10">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="R10">
         <v>2.47</v>
       </c>
       <c r="S10">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T10">
         <v>3.25</v>
       </c>
       <c r="U10">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="V10">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="W10">
         <v>1.11</v>
@@ -1972,31 +1972,31 @@
         <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z10">
         <v>4.25</v>
       </c>
       <c r="AA10">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AB10">
-        <v>2.31</v>
+        <v>2.16</v>
       </c>
       <c r="AC10">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="AD10">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AE10">
         <v>1.18</v>
       </c>
       <c r="AF10">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG10">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AK10">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="AL10">
         <v>0</v>

--- a/jogos_2026-07-29.xlsx
+++ b/jogos_2026-07-29.xlsx
@@ -612,26 +612,26 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
@@ -696,12 +696,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6", "30", "69"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["2", "70"]</t>
         </is>
       </c>
       <c r="AJ2">
@@ -714,28 +714,28 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -775,13 +775,13 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -794,7 +794,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
@@ -859,7 +859,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["37"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -950,14 +950,14 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["85"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1040,28 +1040,28 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -2105,31 +2105,31 @@
         <v>3.75</v>
       </c>
       <c r="O11">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P11">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="Q11">
-        <v>4.8</v>
+        <v>4.25</v>
       </c>
       <c r="R11">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S11">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T11">
         <v>2.93</v>
       </c>
       <c r="U11">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="V11">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X11">
         <v>1.06</v>
@@ -2141,22 +2141,22 @@
         <v>3.24</v>
       </c>
       <c r="AA11">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB11">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC11">
         <v>3.24</v>
       </c>
       <c r="AD11">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE11">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF11">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AG11">
         <v>1.95</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.87</v>
+        <v>1.29</v>
       </c>
       <c r="AK11">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2271,58 +2271,58 @@
         <v>3.75</v>
       </c>
       <c r="P12">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q12">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="R12">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="S12">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="T12">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U12">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="V12">
         <v>1.34</v>
       </c>
       <c r="W12">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z12">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="AA12">
         <v>1.97</v>
       </c>
       <c r="AB12">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AC12">
         <v>3.24</v>
       </c>
       <c r="AD12">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE12">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF12">
         <v>1.85</v>
       </c>
       <c r="AG12">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK12">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,31 +2428,31 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="O13">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P13">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="Q13">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="R13">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="S13">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T13">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="U13">
-        <v>2.9</v>
+        <v>3.33</v>
       </c>
       <c r="V13">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W13">
         <v>1.01</v>
@@ -2461,28 +2461,28 @@
         <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z13">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="AA13">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AB13">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC13">
-        <v>3.92</v>
+        <v>4.2</v>
       </c>
       <c r="AD13">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AE13">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AF13">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AG13">
         <v>1.87</v>
@@ -2501,7 +2501,7 @@
         <v>1.26</v>
       </c>
       <c r="AK13">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,25 +2591,25 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="O14">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="P14">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="Q14">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="R14">
         <v>2.5</v>
       </c>
       <c r="S14">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="T14">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="U14">
         <v>2.17</v>
@@ -2618,37 +2618,37 @@
         <v>1.61</v>
       </c>
       <c r="W14">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X14">
         <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z14">
-        <v>5.1</v>
+        <v>5.29</v>
       </c>
       <c r="AA14">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AB14">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="AC14">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="AD14">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AE14">
         <v>1.18</v>
       </c>
       <c r="AF14">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG14">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK14">
         <v>2.88</v>
@@ -2754,80 +2754,80 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="O15">
-        <v>4.55</v>
+        <v>4.45</v>
       </c>
       <c r="P15">
         <v>4.5</v>
       </c>
       <c r="Q15">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="R15">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="S15">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T15">
         <v>4</v>
       </c>
       <c r="U15">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="V15">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W15">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X15">
         <v>1.02</v>
       </c>
       <c r="Y15">
+        <v>1.11</v>
+      </c>
+      <c r="Z15">
+        <v>5.5</v>
+      </c>
+      <c r="AA15">
+        <v>1.46</v>
+      </c>
+      <c r="AB15">
+        <v>2.38</v>
+      </c>
+      <c r="AC15">
+        <v>2.18</v>
+      </c>
+      <c r="AD15">
+        <v>1.55</v>
+      </c>
+      <c r="AE15">
+        <v>1.21</v>
+      </c>
+      <c r="AF15">
+        <v>1.68</v>
+      </c>
+      <c r="AG15">
+        <v>1.99</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
         <v>1.12</v>
       </c>
-      <c r="Z15">
-        <v>5.1</v>
-      </c>
-      <c r="AA15">
-        <v>1.44</v>
-      </c>
-      <c r="AB15">
-        <v>2.43</v>
-      </c>
-      <c r="AC15">
-        <v>2.15</v>
-      </c>
-      <c r="AD15">
-        <v>1.63</v>
-      </c>
-      <c r="AE15">
-        <v>1.22</v>
-      </c>
-      <c r="AF15">
-        <v>1.61</v>
-      </c>
-      <c r="AG15">
-        <v>2.09</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>1.14</v>
-      </c>
       <c r="AK15">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,65 +2917,65 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.8</v>
+        <v>3.47</v>
       </c>
       <c r="O16">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q16">
-        <v>4.25</v>
+        <v>4.8</v>
       </c>
       <c r="R16">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="S16">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="T16">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="U16">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="V16">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W16">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X16">
         <v>1.05</v>
       </c>
       <c r="Y16">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z16">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="AA16">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="AB16">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AC16">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AD16">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE16">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF16">
+        <v>1.87</v>
+      </c>
+      <c r="AG16">
         <v>1.85</v>
       </c>
-      <c r="AG16">
-        <v>1.86</v>
-      </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AK16">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="O17">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P17">
-        <v>3.95</v>
+        <v>4.95</v>
       </c>
       <c r="Q17">
         <v>2.25</v>
@@ -3095,13 +3095,13 @@
         <v>2.2</v>
       </c>
       <c r="S17">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T17">
-        <v>3.2</v>
+        <v>2.78</v>
       </c>
       <c r="U17">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="V17">
         <v>1.44</v>
@@ -3110,34 +3110,34 @@
         <v>1.07</v>
       </c>
       <c r="X17">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y17">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z17">
-        <v>3.62</v>
+        <v>3.78</v>
       </c>
       <c r="AA17">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AB17">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AC17">
-        <v>3.11</v>
+        <v>2.94</v>
       </c>
       <c r="AD17">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE17">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF17">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AG17">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK17">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.14</v>
+        <v>2.45</v>
       </c>
       <c r="O18">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="P18">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="Q18">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="R18">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="S18">
         <v>1.3</v>
       </c>
       <c r="T18">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="U18">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="V18">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W18">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X18">
         <v>1.04</v>
       </c>
       <c r="Y18">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Z18">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AA18">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AB18">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC18">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AD18">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE18">
         <v>1.08</v>
       </c>
       <c r="AF18">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AG18">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.58</v>
+        <v>1.23</v>
       </c>
       <c r="AK18">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,34 +3406,34 @@
         </is>
       </c>
       <c r="N19">
-        <v>4.68</v>
+        <v>4.3</v>
       </c>
       <c r="O19">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P19">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="Q19">
-        <v>5.4</v>
+        <v>5.17</v>
       </c>
       <c r="R19">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S19">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="T19">
-        <v>2.74</v>
+        <v>3.3</v>
       </c>
       <c r="U19">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="V19">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="W19">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X19">
         <v>1.03</v>
@@ -3442,28 +3442,28 @@
         <v>1.34</v>
       </c>
       <c r="Z19">
-        <v>3.05</v>
+        <v>4.05</v>
       </c>
       <c r="AA19">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="AB19">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="AC19">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="AD19">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AE19">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF19">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AG19">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AK19">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AL19">
         <v>0</v>

--- a/jogos_2026-07-29.xlsx
+++ b/jogos_2026-07-29.xlsx
@@ -1101,26 +1101,26 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["95"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["100", "32", "55", "75"]</t>
         </is>
       </c>
       <c r="AJ5">
@@ -1203,28 +1203,28 @@
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1264,26 +1264,26 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+2", "48"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "16"]</t>
         </is>
       </c>
       <c r="AJ6">
@@ -1366,28 +1366,28 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1439,14 +1439,14 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["65", "80"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -1529,28 +1529,28 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1590,16 +1590,16 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+10"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12"]</t>
         </is>
       </c>
       <c r="AJ8">
@@ -1692,28 +1692,28 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1753,26 +1753,26 @@
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3", "45+4", "49", "60", "79"]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -1855,28 +1855,28 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1916,13 +1916,13 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1931,11 +1931,11 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["44"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["51"]</t>
         </is>
       </c>
       <c r="AJ10">
@@ -2018,28 +2018,28 @@
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
